--- a/Lab 3/Malvern Data/2026_SedStrat_MalvernData.xlsx
+++ b/Lab 3/Malvern Data/2026_SedStrat_MalvernData.xlsx
@@ -1,42 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ethanhoff/Documents/School/FA26/GEO 3550/Lab 3/Malvern Data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{0D8421CB-34BD-F447-830D-C49A56B0F5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{8717AA19-5410-4E32-A579-1CB09D5ACCCA}"/>
+    <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="2026_SedStrat_MalvernData" sheetId="1" r:id="rId1"/>
+    <sheet r:id="rId1" name="2026_SedStrat_MalvernData" sheetId="1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t>Sample Name</t>
   </si>
@@ -131,15 +130,60 @@
     <t>Operator Notes</t>
   </si>
   <si>
-    <t>SedStrat2026Group2</t>
+    <t>2026SedStratGrp1</t>
+  </si>
+  <si>
+    <t>Dirt SOP 3 times</t>
+  </si>
+  <si>
+    <t>Malvern_User</t>
+  </si>
+  <si>
+    <t>Thursday, September 17, 2026 1:51:36 PM</t>
+  </si>
+  <si>
+    <t>Thursday, September 17, 2026 1:51:37 PM</t>
+  </si>
+  <si>
+    <t>Dirt</t>
+  </si>
+  <si>
+    <t>Water</t>
+  </si>
+  <si>
+    <t>Hydro 2000MU (A)</t>
+  </si>
+  <si>
+    <t>General purpose</t>
+  </si>
+  <si>
+    <t>Off</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>Thursday, September 17, 2026 1:52:14 PM</t>
+  </si>
+  <si>
+    <t>Thursday, September 17, 2026 1:52:15 PM</t>
+  </si>
+  <si>
+    <t>Thursday, September 17, 2026 1:52:52 PM</t>
+  </si>
+  <si>
+    <t>Thursday, September 17, 2026 1:52:53 PM</t>
+  </si>
+  <si>
+    <t>Lab Group 1</t>
+  </si>
+  <si>
+    <t>SedStrat2026Grp2</t>
   </si>
   <si>
     <t>Silt SOP 3 times</t>
   </si>
   <si>
-    <t>Malvern_User</t>
-  </si>
-  <si>
     <t>Thursday, September 17, 2026 1:11:54 PM</t>
   </si>
   <si>
@@ -149,21 +193,6 @@
     <t>silt</t>
   </si>
   <si>
-    <t>Water</t>
-  </si>
-  <si>
-    <t>Hydro 2000MU (A)</t>
-  </si>
-  <si>
-    <t>General purpose</t>
-  </si>
-  <si>
-    <t>Off</t>
-  </si>
-  <si>
-    <t>Volume</t>
-  </si>
-  <si>
     <t>Thursday, September 17, 2026 1:12:32 PM</t>
   </si>
   <si>
@@ -176,10 +205,10 @@
     <t>Thursday, September 17, 2026 1:13:11 PM</t>
   </si>
   <si>
-    <t>SedStrat2026Group3</t>
-  </si>
-  <si>
-    <t>Dirt SOP 3 times</t>
+    <t>Lab Group 2</t>
+  </si>
+  <si>
+    <t>SedStrat2026Grp3</t>
   </si>
   <si>
     <t>Thursday, September 17, 2026 1:24:55 PM</t>
@@ -188,9 +217,6 @@
     <t>Thursday, September 17, 2026 1:24:56 PM</t>
   </si>
   <si>
-    <t>Dirt</t>
-  </si>
-  <si>
     <t>Thursday, September 17, 2026 1:25:32 PM</t>
   </si>
   <si>
@@ -203,46 +229,20 @@
     <t>Thursday, September 17, 2026 1:26:11 PM</t>
   </si>
   <si>
-    <t>2026SedStratGroup1</t>
-  </si>
-  <si>
-    <t>Thursday, September 17, 2026 1:51:36 PM</t>
-  </si>
-  <si>
-    <t>Thursday, September 17, 2026 1:51:37 PM</t>
-  </si>
-  <si>
-    <t>Thursday, September 17, 2026 1:52:14 PM</t>
-  </si>
-  <si>
-    <t>Thursday, September 17, 2026 1:52:15 PM</t>
-  </si>
-  <si>
-    <t>Thursday, September 17, 2026 1:52:52 PM</t>
-  </si>
-  <si>
-    <t>Thursday, September 17, 2026 1:52:53 PM</t>
-  </si>
-  <si>
-    <t>AVERAGE GROUP 2</t>
-  </si>
-  <si>
-    <t>AVERAGE GROUP 3</t>
-  </si>
-  <si>
-    <t>AVERAGE GROUP 1</t>
+    <t>Group 3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="1">
     <font>
+      <b val="0"/>
+      <i val="0"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -263,26 +263,42 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+  <bag type="DXFComplements" extRef="DXFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -328,7 +344,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -380,7 +396,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -432,7 +448,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -441,151 +457,175 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42FDB74E-EC67-4E2F-B206-20D64058FCFC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{6234606E-39E7-47EA-8B0F-133B4D4F6EC6}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:EA20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" defaultColWidth="8.8515625" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -680,57 +720,57 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="2" ht="15" customHeight="1">
       <c r="AD2">
         <v>0.01</v>
       </c>
       <c r="AE2">
-        <v>1.1481999999999999E-2</v>
+        <v>0.011482</v>
       </c>
       <c r="AF2">
-        <v>1.3183E-2</v>
+        <v>0.013183</v>
       </c>
       <c r="AG2">
-        <v>1.5136E-2</v>
+        <v>0.015136</v>
       </c>
       <c r="AH2">
-        <v>1.7378000000000001E-2</v>
+        <v>0.017378</v>
       </c>
       <c r="AI2">
-        <v>1.9952999999999999E-2</v>
+        <v>0.019953</v>
       </c>
       <c r="AJ2">
-        <v>2.2908999999999999E-2</v>
+        <v>0.022909</v>
       </c>
       <c r="AK2">
-        <v>2.6303E-2</v>
+        <v>0.026303</v>
       </c>
       <c r="AL2">
-        <v>3.0200000000000001E-2</v>
+        <v>0.0302</v>
       </c>
       <c r="AM2">
-        <v>3.4674000000000003E-2</v>
+        <v>0.034674</v>
       </c>
       <c r="AN2">
-        <v>3.9810999999999999E-2</v>
+        <v>0.039811</v>
       </c>
       <c r="AO2">
-        <v>4.5709E-2</v>
+        <v>0.045709</v>
       </c>
       <c r="AP2">
-        <v>5.2481E-2</v>
+        <v>0.052481</v>
       </c>
       <c r="AQ2">
-        <v>6.0255999999999997E-2</v>
+        <v>0.060256</v>
       </c>
       <c r="AR2">
-        <v>6.9182999999999995E-2</v>
+        <v>0.069183</v>
       </c>
       <c r="AS2">
-        <v>7.9433000000000004E-2</v>
+        <v>0.079433</v>
       </c>
       <c r="AT2">
-        <v>9.1201000000000004E-2</v>
+        <v>0.091201</v>
       </c>
       <c r="AU2">
         <v>0.104713</v>
@@ -739,97 +779,97 @@
         <v>0.120226</v>
       </c>
       <c r="AW2">
-        <v>0.13803799999999999</v>
+        <v>0.138038</v>
       </c>
       <c r="AX2">
-        <v>0.15848899999999999</v>
+        <v>0.158489</v>
       </c>
       <c r="AY2">
-        <v>0.18196999999999999</v>
+        <v>0.18197</v>
       </c>
       <c r="AZ2">
         <v>0.20893</v>
       </c>
       <c r="BA2">
-        <v>0.23988300000000001</v>
+        <v>0.239883</v>
       </c>
       <c r="BB2">
-        <v>0.27542299999999997</v>
+        <v>0.275423</v>
       </c>
       <c r="BC2">
-        <v>0.31622800000000001</v>
+        <v>0.316228</v>
       </c>
       <c r="BD2">
-        <v>0.36307800000000001</v>
+        <v>0.363078</v>
       </c>
       <c r="BE2">
-        <v>0.41686899999999999</v>
+        <v>0.416869</v>
       </c>
       <c r="BF2">
         <v>0.47863</v>
       </c>
       <c r="BG2">
-        <v>0.54954099999999995</v>
+        <v>0.549541</v>
       </c>
       <c r="BH2">
-        <v>0.63095699999999999</v>
+        <v>0.630957</v>
       </c>
       <c r="BI2">
-        <v>0.72443599999999997</v>
+        <v>0.724436</v>
       </c>
       <c r="BJ2">
-        <v>0.83176399999999995</v>
+        <v>0.831764</v>
       </c>
       <c r="BK2">
-        <v>0.95499299999999998</v>
+        <v>0.954993</v>
       </c>
       <c r="BL2">
-        <v>1.0964780000000001</v>
+        <v>1.096478</v>
       </c>
       <c r="BM2">
-        <v>1.2589250000000001</v>
+        <v>1.258925</v>
       </c>
       <c r="BN2">
-        <v>1.4454400000000001</v>
+        <v>1.44544</v>
       </c>
       <c r="BO2">
-        <v>1.6595869999999999</v>
+        <v>1.659587</v>
       </c>
       <c r="BP2">
-        <v>1.9054610000000001</v>
+        <v>1.905461</v>
       </c>
       <c r="BQ2">
-        <v>2.1877620000000002</v>
+        <v>2.187762</v>
       </c>
       <c r="BR2">
-        <v>2.5118860000000001</v>
+        <v>2.511886</v>
       </c>
       <c r="BS2">
-        <v>2.8840309999999998</v>
+        <v>2.884031</v>
       </c>
       <c r="BT2">
-        <v>3.3113109999999999</v>
+        <v>3.311311</v>
       </c>
       <c r="BU2">
-        <v>3.8018939999999999</v>
+        <v>3.801894</v>
       </c>
       <c r="BV2">
-        <v>4.3651580000000001</v>
+        <v>4.365158</v>
       </c>
       <c r="BW2">
-        <v>5.0118720000000003</v>
+        <v>5.011872</v>
       </c>
       <c r="BX2">
-        <v>5.7543990000000003</v>
+        <v>5.754399</v>
       </c>
       <c r="BY2">
-        <v>6.6069339999999999</v>
+        <v>6.606934</v>
       </c>
       <c r="BZ2">
-        <v>7.5857760000000001</v>
+        <v>7.585776</v>
       </c>
       <c r="CA2">
-        <v>8.7096359999999997</v>
+        <v>8.709636</v>
       </c>
       <c r="CB2">
         <v>10</v>
@@ -838,49 +878,49 @@
         <v>11.481536</v>
       </c>
       <c r="CD2">
-        <v>13.182567000000001</v>
+        <v>13.182567</v>
       </c>
       <c r="CE2">
         <v>15.135612</v>
       </c>
       <c r="CF2">
-        <v>17.378008000000001</v>
+        <v>17.378008</v>
       </c>
       <c r="CG2">
-        <v>19.952622999999999</v>
+        <v>19.952623</v>
       </c>
       <c r="CH2">
-        <v>22.908677000000001</v>
+        <v>22.908677</v>
       </c>
       <c r="CI2">
-        <v>26.302679999999999</v>
+        <v>26.30268</v>
       </c>
       <c r="CJ2">
         <v>30.199517</v>
       </c>
       <c r="CK2">
-        <v>34.673684999999999</v>
+        <v>34.673685</v>
       </c>
       <c r="CL2">
-        <v>39.810716999999997</v>
+        <v>39.810717</v>
       </c>
       <c r="CM2">
-        <v>45.708818999999998</v>
+        <v>45.708819</v>
       </c>
       <c r="CN2">
-        <v>52.480746000000003</v>
+        <v>52.480746</v>
       </c>
       <c r="CO2">
-        <v>60.255958999999997</v>
+        <v>60.255959</v>
       </c>
       <c r="CP2">
-        <v>69.183097000000004</v>
+        <v>69.183097</v>
       </c>
       <c r="CQ2">
-        <v>79.432822999999999</v>
+        <v>79.432823</v>
       </c>
       <c r="CR2">
-        <v>91.201083999999994</v>
+        <v>91.201084</v>
       </c>
       <c r="CS2">
         <v>104.712855</v>
@@ -889,120 +929,120 @@
         <v>120.226443</v>
       </c>
       <c r="CU2">
-        <v>138.03842599999999</v>
+        <v>138.038426</v>
       </c>
       <c r="CV2">
-        <v>158.48931899999999</v>
+        <v>158.489319</v>
       </c>
       <c r="CW2">
-        <v>181.97008600000001</v>
+        <v>181.970086</v>
       </c>
       <c r="CX2">
-        <v>208.92961299999999</v>
+        <v>208.929613</v>
       </c>
       <c r="CY2">
-        <v>239.88329200000001</v>
+        <v>239.883292</v>
       </c>
       <c r="CZ2">
-        <v>275.42286999999999</v>
+        <v>275.42287</v>
       </c>
       <c r="DA2">
-        <v>316.22776599999997</v>
+        <v>316.227766</v>
       </c>
       <c r="DB2">
-        <v>363.07805500000001</v>
+        <v>363.078055</v>
       </c>
       <c r="DC2">
-        <v>416.86938300000003</v>
+        <v>416.869383</v>
       </c>
       <c r="DD2">
-        <v>478.63009199999999</v>
+        <v>478.630092</v>
       </c>
       <c r="DE2">
-        <v>549.54087400000003</v>
+        <v>549.540874</v>
       </c>
       <c r="DF2">
-        <v>630.95734400000003</v>
+        <v>630.957344</v>
       </c>
       <c r="DG2">
-        <v>724.43596000000002</v>
+        <v>724.43596</v>
       </c>
       <c r="DH2">
-        <v>831.76377100000002</v>
+        <v>831.763771</v>
       </c>
       <c r="DI2">
-        <v>954.99258599999996</v>
+        <v>954.992586</v>
       </c>
       <c r="DJ2">
         <v>1096.478196</v>
       </c>
       <c r="DK2">
-        <v>1258.9254120000001</v>
+        <v>1258.925412</v>
       </c>
       <c r="DL2">
-        <v>1445.4397710000001</v>
+        <v>1445.439771</v>
       </c>
       <c r="DM2">
-        <v>1659.5869070000001</v>
+        <v>1659.586907</v>
       </c>
       <c r="DN2">
         <v>1905.460718</v>
       </c>
       <c r="DO2">
-        <v>2187.7616240000002</v>
+        <v>2187.761624</v>
       </c>
       <c r="DP2">
-        <v>2511.8864319999998</v>
+        <v>2511.886432</v>
       </c>
       <c r="DQ2">
-        <v>2884.0315030000002</v>
+        <v>2884.031503</v>
       </c>
       <c r="DR2">
-        <v>3311.3112150000002</v>
+        <v>3311.311215</v>
       </c>
       <c r="DS2">
         <v>3801.893963</v>
       </c>
       <c r="DT2">
-        <v>4365.1583220000002</v>
+        <v>4365.158322</v>
       </c>
       <c r="DU2">
-        <v>5011.8723360000004</v>
+        <v>5011.872336</v>
       </c>
       <c r="DV2">
-        <v>5754.3993730000002</v>
+        <v>5754.399373</v>
       </c>
       <c r="DW2">
-        <v>6606.9344799999999</v>
+        <v>6606.93448</v>
       </c>
       <c r="DX2">
-        <v>7585.7757499999998</v>
+        <v>7585.77575</v>
       </c>
       <c r="DY2">
-        <v>8709.6358999999993</v>
+        <v>8709.6359</v>
       </c>
       <c r="DZ2">
         <v>10000</v>
       </c>
     </row>
-    <row r="3" spans="1:131" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>55</v>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
         <v>33</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="G3" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="H3" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="I3">
         <v>1.56</v>
@@ -1035,10 +1075,10 @@
         <v>9.11</v>
       </c>
       <c r="S3">
-        <v>1.2829999999999999</v>
+        <v>1.283</v>
       </c>
       <c r="T3">
-        <v>1.14E-2</v>
+        <v>0.0114</v>
       </c>
       <c r="U3">
         <v>4.71</v>
@@ -1053,7 +1093,7 @@
         <v>1.8</v>
       </c>
       <c r="Y3">
-        <v>0.70499999999999996</v>
+        <v>0.705</v>
       </c>
       <c r="Z3">
         <v>8.51</v>
@@ -1062,10 +1102,10 @@
         <v>3.617</v>
       </c>
       <c r="AB3">
-        <v>31.283999999999999</v>
+        <v>31.284</v>
       </c>
       <c r="AC3">
-        <v>150.96199999999999</v>
+        <v>150.962</v>
       </c>
       <c r="AE3">
         <v>0</v>
@@ -1158,49 +1198,49 @@
         <v>0.423489</v>
       </c>
       <c r="BI3">
-        <v>0.52540699999999996</v>
+        <v>0.525407</v>
       </c>
       <c r="BJ3">
-        <v>0.59985999999999995</v>
+        <v>0.59986</v>
       </c>
       <c r="BK3">
-        <v>0.61881600000000003</v>
+        <v>0.618816</v>
       </c>
       <c r="BL3">
-        <v>0.61102100000000004</v>
+        <v>0.611021</v>
       </c>
       <c r="BM3">
-        <v>0.59554300000000004</v>
+        <v>0.595543</v>
       </c>
       <c r="BN3">
-        <v>0.59644900000000001</v>
+        <v>0.596449</v>
       </c>
       <c r="BO3">
-        <v>0.62820699999999996</v>
+        <v>0.628207</v>
       </c>
       <c r="BP3">
-        <v>0.69293099999999996</v>
+        <v>0.692931</v>
       </c>
       <c r="BQ3">
         <v>0.780864</v>
       </c>
       <c r="BR3">
-        <v>0.88075700000000001</v>
+        <v>0.880757</v>
       </c>
       <c r="BS3">
-        <v>0.98505100000000001</v>
+        <v>0.985051</v>
       </c>
       <c r="BT3">
         <v>1.089561</v>
       </c>
       <c r="BU3">
-        <v>1.1926540000000001</v>
+        <v>1.192654</v>
       </c>
       <c r="BV3">
         <v>1.294678</v>
       </c>
       <c r="BW3">
-        <v>1.4004209999999999</v>
+        <v>1.400421</v>
       </c>
       <c r="BX3">
         <v>1.514049</v>
@@ -1209,109 +1249,109 @@
         <v>1.644622</v>
       </c>
       <c r="BZ3">
-        <v>1.7961400000000001</v>
+        <v>1.79614</v>
       </c>
       <c r="CA3">
         <v>1.977481</v>
       </c>
       <c r="CB3">
-        <v>2.1858179999999998</v>
+        <v>2.185818</v>
       </c>
       <c r="CC3">
-        <v>2.4256709999999999</v>
+        <v>2.425671</v>
       </c>
       <c r="CD3">
-        <v>2.6835870000000002</v>
+        <v>2.683587</v>
       </c>
       <c r="CE3">
-        <v>2.9579949999999999</v>
+        <v>2.957995</v>
       </c>
       <c r="CF3">
-        <v>3.2309540000000001</v>
+        <v>3.230954</v>
       </c>
       <c r="CG3">
-        <v>3.4982660000000001</v>
+        <v>3.498266</v>
       </c>
       <c r="CH3">
-        <v>3.7449439999999998</v>
+        <v>3.744944</v>
       </c>
       <c r="CI3">
         <v>3.966526</v>
       </c>
       <c r="CJ3">
-        <v>4.1513580000000001</v>
+        <v>4.151358</v>
       </c>
       <c r="CK3">
-        <v>4.2920049999999996</v>
+        <v>4.292005</v>
       </c>
       <c r="CL3">
-        <v>4.3765390000000002</v>
+        <v>4.376539</v>
       </c>
       <c r="CM3">
-        <v>4.3939779999999997</v>
+        <v>4.393978</v>
       </c>
       <c r="CN3">
-        <v>4.3337709999999996</v>
+        <v>4.333771</v>
       </c>
       <c r="CO3">
-        <v>4.1893250000000002</v>
+        <v>4.189325</v>
       </c>
       <c r="CP3">
-        <v>3.9597600000000002</v>
+        <v>3.95976</v>
       </c>
       <c r="CQ3">
-        <v>3.6556289999999998</v>
+        <v>3.655629</v>
       </c>
       <c r="CR3">
         <v>3.289965</v>
       </c>
       <c r="CS3">
-        <v>2.8908740000000002</v>
+        <v>2.890874</v>
       </c>
       <c r="CT3">
-        <v>2.4762900000000001</v>
+        <v>2.47629</v>
       </c>
       <c r="CU3">
-        <v>2.0792760000000001</v>
+        <v>2.079276</v>
       </c>
       <c r="CV3">
-        <v>1.7115959999999999</v>
+        <v>1.711596</v>
       </c>
       <c r="CW3">
         <v>1.398887</v>
       </c>
       <c r="CX3">
-        <v>1.1406970000000001</v>
+        <v>1.140697</v>
       </c>
       <c r="CY3">
-        <v>0.94679199999999997</v>
+        <v>0.946792</v>
       </c>
       <c r="CZ3">
-        <v>0.80635999999999997</v>
+        <v>0.80636</v>
       </c>
       <c r="DA3">
-        <v>0.71502699999999997</v>
+        <v>0.715027</v>
       </c>
       <c r="DB3">
-        <v>0.66099799999999997</v>
+        <v>0.660998</v>
       </c>
       <c r="DC3">
         <v>0.634436</v>
       </c>
       <c r="DD3">
-        <v>0.62187400000000004</v>
+        <v>0.621874</v>
       </c>
       <c r="DE3">
-        <v>0.60852200000000001</v>
+        <v>0.608522</v>
       </c>
       <c r="DF3">
-        <v>0.57996199999999998</v>
+        <v>0.579962</v>
       </c>
       <c r="DG3">
-        <v>0.53179699999999996</v>
+        <v>0.531797</v>
       </c>
       <c r="DH3">
-        <v>0.45656799999999997</v>
+        <v>0.456568</v>
       </c>
       <c r="DI3">
         <v>0.333594</v>
@@ -1368,24 +1408,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:131" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>55</v>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
         <v>33</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="G4" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="H4" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="I4">
         <v>1.56</v>
@@ -1415,13 +1455,13 @@
         <v>40</v>
       </c>
       <c r="R4">
-        <v>8.9499999999999993</v>
+        <v>8.95</v>
       </c>
       <c r="S4">
-        <v>1.2769999999999999</v>
+        <v>1.277</v>
       </c>
       <c r="T4">
-        <v>1.12E-2</v>
+        <v>0.0112</v>
       </c>
       <c r="U4">
         <v>4.617</v>
@@ -1430,25 +1470,25 @@
         <v>41</v>
       </c>
       <c r="W4">
-        <v>65.918999999999997</v>
+        <v>65.919</v>
       </c>
       <c r="X4">
         <v>1.71</v>
       </c>
       <c r="Y4">
-        <v>0.70499999999999996</v>
+        <v>0.705</v>
       </c>
       <c r="Z4">
-        <v>8.5120000000000005</v>
+        <v>8.512</v>
       </c>
       <c r="AA4">
-        <v>3.6309999999999998</v>
+        <v>3.631</v>
       </c>
       <c r="AB4">
-        <v>30.943999999999999</v>
+        <v>30.944</v>
       </c>
       <c r="AC4">
-        <v>146.50200000000001</v>
+        <v>146.502</v>
       </c>
       <c r="AE4">
         <v>0</v>
@@ -1541,40 +1581,40 @@
         <v>0.420543</v>
       </c>
       <c r="BI4">
-        <v>0.52326600000000001</v>
+        <v>0.523266</v>
       </c>
       <c r="BJ4">
-        <v>0.59769399999999995</v>
+        <v>0.597694</v>
       </c>
       <c r="BK4">
-        <v>0.61657300000000004</v>
+        <v>0.616573</v>
       </c>
       <c r="BL4">
-        <v>0.60845700000000003</v>
+        <v>0.608457</v>
       </c>
       <c r="BM4">
-        <v>0.59263600000000005</v>
+        <v>0.592636</v>
       </c>
       <c r="BN4">
-        <v>0.59327700000000005</v>
+        <v>0.593277</v>
       </c>
       <c r="BO4">
-        <v>0.62495599999999996</v>
+        <v>0.624956</v>
       </c>
       <c r="BP4">
-        <v>0.68981899999999996</v>
+        <v>0.689819</v>
       </c>
       <c r="BQ4">
-        <v>0.77810000000000001</v>
+        <v>0.7781</v>
       </c>
       <c r="BR4">
-        <v>0.87854299999999996</v>
+        <v>0.878543</v>
       </c>
       <c r="BS4">
-        <v>0.98360499999999995</v>
+        <v>0.983605</v>
       </c>
       <c r="BT4">
-        <v>1.0891219999999999</v>
+        <v>1.089122</v>
       </c>
       <c r="BU4">
         <v>1.1935</v>
@@ -1589,115 +1629,115 @@
         <v>1.52085</v>
       </c>
       <c r="BY4">
-        <v>1.6542460000000001</v>
+        <v>1.654246</v>
       </c>
       <c r="BZ4">
         <v>1.808954</v>
       </c>
       <c r="CA4">
-        <v>1.9938800000000001</v>
+        <v>1.99388</v>
       </c>
       <c r="CB4">
-        <v>2.2060409999999999</v>
+        <v>2.206041</v>
       </c>
       <c r="CC4">
-        <v>2.4499960000000001</v>
+        <v>2.449996</v>
       </c>
       <c r="CD4">
-        <v>2.7120690000000001</v>
+        <v>2.712069</v>
       </c>
       <c r="CE4">
-        <v>2.9906830000000002</v>
+        <v>2.990683</v>
       </c>
       <c r="CF4">
-        <v>3.2675920000000001</v>
+        <v>3.267592</v>
       </c>
       <c r="CG4">
-        <v>3.5383779999999998</v>
+        <v>3.538378</v>
       </c>
       <c r="CH4">
-        <v>3.7875100000000002</v>
+        <v>3.78751</v>
       </c>
       <c r="CI4">
-        <v>4.0099609999999997</v>
+        <v>4.009961</v>
       </c>
       <c r="CJ4">
-        <v>4.1934610000000001</v>
+        <v>4.193461</v>
       </c>
       <c r="CK4">
-        <v>4.3301030000000003</v>
+        <v>4.330103</v>
       </c>
       <c r="CL4">
-        <v>4.4078280000000003</v>
+        <v>4.407828</v>
       </c>
       <c r="CM4">
-        <v>4.4159410000000001</v>
+        <v>4.415941</v>
       </c>
       <c r="CN4">
-        <v>4.3447789999999999</v>
+        <v>4.344779</v>
       </c>
       <c r="CO4">
-        <v>4.1891800000000003</v>
+        <v>4.18918</v>
       </c>
       <c r="CP4">
-        <v>3.9499520000000001</v>
+        <v>3.949952</v>
       </c>
       <c r="CQ4">
-        <v>3.6393610000000001</v>
+        <v>3.639361</v>
       </c>
       <c r="CR4">
-        <v>3.2715649999999998</v>
+        <v>3.271565</v>
       </c>
       <c r="CS4">
-        <v>2.8751329999999999</v>
+        <v>2.875133</v>
       </c>
       <c r="CT4">
         <v>2.467581</v>
       </c>
       <c r="CU4">
-        <v>2.0805769999999999</v>
+        <v>2.080577</v>
       </c>
       <c r="CV4">
-        <v>1.7244870000000001</v>
+        <v>1.724487</v>
       </c>
       <c r="CW4">
-        <v>1.4230100000000001</v>
+        <v>1.42301</v>
       </c>
       <c r="CX4">
-        <v>1.1745559999999999</v>
+        <v>1.174556</v>
       </c>
       <c r="CY4">
         <v>0.987209</v>
       </c>
       <c r="CZ4">
-        <v>0.84862400000000004</v>
+        <v>0.848624</v>
       </c>
       <c r="DA4">
-        <v>0.75224899999999995</v>
+        <v>0.752249</v>
       </c>
       <c r="DB4">
-        <v>0.68420499999999995</v>
+        <v>0.684205</v>
       </c>
       <c r="DC4">
-        <v>0.63418699999999995</v>
+        <v>0.634187</v>
       </c>
       <c r="DD4">
         <v>0.589974</v>
       </c>
       <c r="DE4">
-        <v>0.54134300000000002</v>
+        <v>0.541343</v>
       </c>
       <c r="DF4">
-        <v>0.47978100000000001</v>
+        <v>0.479781</v>
       </c>
       <c r="DG4">
-        <v>0.40672199999999997</v>
+        <v>0.406722</v>
       </c>
       <c r="DH4">
-        <v>0.32042799999999999</v>
+        <v>0.320428</v>
       </c>
       <c r="DI4">
-        <v>0.21601500000000001</v>
+        <v>0.216015</v>
       </c>
       <c r="DJ4">
         <v>0</v>
@@ -1751,24 +1791,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:131" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>55</v>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
         <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="G5" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="H5" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="I5">
         <v>1.56</v>
@@ -1801,37 +1841,37 @@
         <v>8.84</v>
       </c>
       <c r="S5">
-        <v>1.2729999999999999</v>
+        <v>1.273</v>
       </c>
       <c r="T5">
-        <v>1.12E-2</v>
+        <v>0.0112</v>
       </c>
       <c r="U5">
-        <v>4.6740000000000004</v>
+        <v>4.674</v>
       </c>
       <c r="V5" t="s">
         <v>41</v>
       </c>
       <c r="W5">
-        <v>69.650000000000006</v>
+        <v>69.65</v>
       </c>
       <c r="X5">
         <v>1.82</v>
       </c>
       <c r="Y5">
-        <v>0.69899999999999995</v>
+        <v>0.699</v>
       </c>
       <c r="Z5">
-        <v>8.5890000000000004</v>
+        <v>8.589</v>
       </c>
       <c r="AA5">
-        <v>3.6779999999999999</v>
+        <v>3.678</v>
       </c>
       <c r="AB5">
-        <v>31.167000000000002</v>
+        <v>31.167</v>
       </c>
       <c r="AC5">
-        <v>149.35599999999999</v>
+        <v>149.356</v>
       </c>
       <c r="AE5">
         <v>0</v>
@@ -1921,127 +1961,127 @@
         <v>0.215228</v>
       </c>
       <c r="BH5">
-        <v>0.41426800000000003</v>
+        <v>0.414268</v>
       </c>
       <c r="BI5">
-        <v>0.51672799999999997</v>
+        <v>0.516728</v>
       </c>
       <c r="BJ5">
-        <v>0.59057099999999996</v>
+        <v>0.590571</v>
       </c>
       <c r="BK5">
-        <v>0.60939399999999999</v>
+        <v>0.609394</v>
       </c>
       <c r="BL5">
-        <v>0.60131199999999996</v>
+        <v>0.601312</v>
       </c>
       <c r="BM5">
-        <v>0.58557400000000004</v>
+        <v>0.585574</v>
       </c>
       <c r="BN5">
-        <v>0.58616500000000005</v>
+        <v>0.586165</v>
       </c>
       <c r="BO5">
-        <v>0.61757300000000004</v>
+        <v>0.617573</v>
       </c>
       <c r="BP5">
-        <v>0.68193300000000001</v>
+        <v>0.681933</v>
       </c>
       <c r="BQ5">
-        <v>0.76955899999999999</v>
+        <v>0.769559</v>
       </c>
       <c r="BR5">
         <v>0.869313</v>
       </c>
       <c r="BS5">
-        <v>0.97378699999999996</v>
+        <v>0.973787</v>
       </c>
       <c r="BT5">
         <v>1.078938</v>
       </c>
       <c r="BU5">
-        <v>1.1832499999999999</v>
+        <v>1.18325</v>
       </c>
       <c r="BV5">
-        <v>1.2871170000000001</v>
+        <v>1.287117</v>
       </c>
       <c r="BW5">
-        <v>1.3953720000000001</v>
+        <v>1.395372</v>
       </c>
       <c r="BX5">
-        <v>1.5121290000000001</v>
+        <v>1.512129</v>
       </c>
       <c r="BY5">
-        <v>1.6464570000000001</v>
+        <v>1.646457</v>
       </c>
       <c r="BZ5">
-        <v>1.8022039999999999</v>
+        <v>1.802204</v>
       </c>
       <c r="CA5">
-        <v>1.9882310000000001</v>
+        <v>1.988231</v>
       </c>
       <c r="CB5">
         <v>2.201416</v>
       </c>
       <c r="CC5">
-        <v>2.4461940000000002</v>
+        <v>2.446194</v>
       </c>
       <c r="CD5">
-        <v>2.7086790000000001</v>
+        <v>2.708679</v>
       </c>
       <c r="CE5">
-        <v>2.9871289999999999</v>
+        <v>2.987129</v>
       </c>
       <c r="CF5">
-        <v>3.2631730000000001</v>
+        <v>3.263173</v>
       </c>
       <c r="CG5">
-        <v>3.5323560000000001</v>
+        <v>3.532356</v>
       </c>
       <c r="CH5">
-        <v>3.7793619999999999</v>
+        <v>3.779362</v>
       </c>
       <c r="CI5">
-        <v>3.9996049999999999</v>
+        <v>3.999605</v>
       </c>
       <c r="CJ5">
-        <v>4.1815740000000003</v>
+        <v>4.181574</v>
       </c>
       <c r="CK5">
-        <v>4.3181779999999996</v>
+        <v>4.318178</v>
       </c>
       <c r="CL5">
         <v>4.397983</v>
       </c>
       <c r="CM5">
-        <v>4.4104330000000003</v>
+        <v>4.410433</v>
       </c>
       <c r="CN5">
-        <v>4.3453480000000004</v>
+        <v>4.345348</v>
       </c>
       <c r="CO5">
-        <v>4.1964009999999998</v>
+        <v>4.196401</v>
       </c>
       <c r="CP5">
         <v>3.962831</v>
       </c>
       <c r="CQ5">
-        <v>3.6551070000000001</v>
+        <v>3.655107</v>
       </c>
       <c r="CR5">
-        <v>3.2858239999999999</v>
+        <v>3.285824</v>
       </c>
       <c r="CS5">
-        <v>2.8824890000000001</v>
+        <v>2.882489</v>
       </c>
       <c r="CT5">
-        <v>2.4621360000000001</v>
+        <v>2.462136</v>
       </c>
       <c r="CU5">
-        <v>2.0573540000000001</v>
+        <v>2.057354</v>
       </c>
       <c r="CV5">
-        <v>1.6799109999999999</v>
+        <v>1.679911</v>
       </c>
       <c r="CW5">
         <v>1.357251</v>
@@ -2050,37 +2090,37 @@
         <v>1.091507</v>
       </c>
       <c r="CY5">
-        <v>0.89571999999999996</v>
+        <v>0.89572</v>
       </c>
       <c r="CZ5">
-        <v>0.76064699999999996</v>
+        <v>0.760647</v>
       </c>
       <c r="DA5">
-        <v>0.68095000000000006</v>
+        <v>0.68095</v>
       </c>
       <c r="DB5">
-        <v>0.64222699999999999</v>
+        <v>0.642227</v>
       </c>
       <c r="DC5">
-        <v>0.63103600000000004</v>
+        <v>0.631036</v>
       </c>
       <c r="DD5">
-        <v>0.63166100000000003</v>
+        <v>0.631661</v>
       </c>
       <c r="DE5">
-        <v>0.62800299999999998</v>
+        <v>0.628003</v>
       </c>
       <c r="DF5">
-        <v>0.60545300000000002</v>
+        <v>0.605453</v>
       </c>
       <c r="DG5">
-        <v>0.55973499999999998</v>
+        <v>0.559735</v>
       </c>
       <c r="DH5">
-        <v>0.48316799999999999</v>
+        <v>0.483168</v>
       </c>
       <c r="DI5">
-        <v>0.35405500000000001</v>
+        <v>0.354055</v>
       </c>
       <c r="DJ5">
         <v>0</v>
@@ -2134,61 +2174,61 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:131" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>64</v>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="BG6">
-        <f t="shared" ref="AF6:CQ6" si="0">AVERAGE(BG3:BG5)</f>
+        <f t="shared" si="0" ref="BG6:DZ6">AVERAGE(BG3:BG5)</f>
         <v>0.21903733333333333</v>
       </c>
       <c r="BH6">
         <f t="shared" si="0"/>
-        <v>0.41943333333333332</v>
+        <v>0.4194333333333333</v>
       </c>
       <c r="BI6">
         <f t="shared" si="0"/>
-        <v>0.52180033333333331</v>
+        <v>0.5218003333333333</v>
       </c>
       <c r="BJ6">
         <f t="shared" si="0"/>
-        <v>0.59604166666666658</v>
+        <v>0.5960416666666666</v>
       </c>
       <c r="BK6">
         <f t="shared" si="0"/>
-        <v>0.61492766666666665</v>
+        <v>0.6149276666666667</v>
       </c>
       <c r="BL6">
         <f t="shared" si="0"/>
-        <v>0.60693000000000008</v>
+        <v>0.6069300000000001</v>
       </c>
       <c r="BM6">
         <f t="shared" si="0"/>
-        <v>0.59125100000000008</v>
+        <v>0.5912510000000001</v>
       </c>
       <c r="BN6">
         <f t="shared" si="0"/>
-        <v>0.59196366666666667</v>
+        <v>0.5919636666666667</v>
       </c>
       <c r="BO6">
         <f t="shared" si="0"/>
-        <v>0.62357866666666661</v>
+        <v>0.6235786666666666</v>
       </c>
       <c r="BP6">
         <f t="shared" si="0"/>
-        <v>0.68822766666666668</v>
+        <v>0.6882276666666667</v>
       </c>
       <c r="BQ6">
         <f t="shared" si="0"/>
-        <v>0.77617433333333341</v>
+        <v>0.7761743333333334</v>
       </c>
       <c r="BR6">
         <f t="shared" si="0"/>
-        <v>0.87620433333333336</v>
+        <v>0.8762043333333334</v>
       </c>
       <c r="BS6">
         <f t="shared" si="0"/>
-        <v>0.98081433333333334</v>
+        <v>0.9808143333333333</v>
       </c>
       <c r="BT6">
         <f t="shared" si="0"/>
@@ -2232,7 +2272,7 @@
       </c>
       <c r="CD6">
         <f t="shared" si="0"/>
-        <v>2.7014450000000001</v>
+        <v>2.701445</v>
       </c>
       <c r="CE6">
         <f t="shared" si="0"/>
@@ -2240,7 +2280,7 @@
       </c>
       <c r="CF6">
         <f t="shared" si="0"/>
-        <v>3.2539063333333331</v>
+        <v>3.253906333333333</v>
       </c>
       <c r="CG6">
         <f t="shared" si="0"/>
@@ -2256,27 +2296,27 @@
       </c>
       <c r="CJ6">
         <f t="shared" si="0"/>
-        <v>4.1754643333333341</v>
+        <v>4.175464333333334</v>
       </c>
       <c r="CK6">
         <f t="shared" si="0"/>
-        <v>4.3134286666666668</v>
+        <v>4.313428666666667</v>
       </c>
       <c r="CL6">
         <f t="shared" si="0"/>
-        <v>4.3941166666666662</v>
+        <v>4.394116666666666</v>
       </c>
       <c r="CM6">
         <f t="shared" si="0"/>
-        <v>4.4067840000000009</v>
+        <v>4.406784000000001</v>
       </c>
       <c r="CN6">
         <f t="shared" si="0"/>
-        <v>4.3412993333333327</v>
+        <v>4.341299333333333</v>
       </c>
       <c r="CO6">
         <f t="shared" si="0"/>
-        <v>4.1916353333333332</v>
+        <v>4.191635333333333</v>
       </c>
       <c r="CP6">
         <f t="shared" si="0"/>
@@ -2287,83 +2327,83 @@
         <v>3.6500323333333333</v>
       </c>
       <c r="CR6">
-        <f t="shared" ref="CR6:DZ6" si="1">AVERAGE(CR3:CR5)</f>
-        <v>3.2824513333333329</v>
+        <f t="shared" si="0"/>
+        <v>3.282451333333333</v>
       </c>
       <c r="CS6">
-        <f t="shared" si="1"/>
-        <v>2.8828320000000001</v>
+        <f t="shared" si="0"/>
+        <v>2.882832</v>
       </c>
       <c r="CT6">
-        <f t="shared" si="1"/>
-        <v>2.4686689999999998</v>
+        <f t="shared" si="0"/>
+        <v>2.468669</v>
       </c>
       <c r="CU6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2.0724023333333332</v>
       </c>
       <c r="CV6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.7053313333333333</v>
       </c>
       <c r="CW6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.3930493333333331</v>
       </c>
       <c r="CX6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.1355866666666667</v>
       </c>
       <c r="CY6">
-        <f t="shared" si="1"/>
-        <v>0.94324033333333324</v>
+        <f t="shared" si="0"/>
+        <v>0.9432403333333332</v>
       </c>
       <c r="CZ6">
-        <f t="shared" si="1"/>
-        <v>0.80521033333333325</v>
+        <f t="shared" si="0"/>
+        <v>0.8052103333333333</v>
       </c>
       <c r="DA6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.7160753333333334</v>
       </c>
       <c r="DB6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.6624766666666666</v>
       </c>
       <c r="DC6">
-        <f t="shared" si="1"/>
-        <v>0.63321966666666663</v>
+        <f t="shared" si="0"/>
+        <v>0.6332196666666666</v>
       </c>
       <c r="DD6">
-        <f t="shared" si="1"/>
-        <v>0.61450300000000002</v>
+        <f t="shared" si="0"/>
+        <v>0.614503</v>
       </c>
       <c r="DE6">
-        <f t="shared" si="1"/>
-        <v>0.59262266666666674</v>
+        <f t="shared" si="0"/>
+        <v>0.5926226666666667</v>
       </c>
       <c r="DF6">
-        <f t="shared" si="1"/>
-        <v>0.55506533333333341</v>
+        <f t="shared" si="0"/>
+        <v>0.5550653333333334</v>
       </c>
       <c r="DG6">
-        <f t="shared" si="1"/>
-        <v>0.49941799999999992</v>
+        <f t="shared" si="0"/>
+        <v>0.4994179999999999</v>
       </c>
       <c r="DH6">
-        <f t="shared" si="1"/>
-        <v>0.42005466666666669</v>
+        <f t="shared" si="0"/>
+        <v>0.4200546666666667</v>
       </c>
       <c r="DI6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.30122133333333334</v>
       </c>
       <c r="DZ6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="8" ht="15" customHeight="1">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -2458,57 +2498,57 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="9" ht="15" customHeight="1">
       <c r="AD9">
         <v>0.01</v>
       </c>
       <c r="AE9">
-        <v>1.1481999999999999E-2</v>
+        <v>0.011482</v>
       </c>
       <c r="AF9">
-        <v>1.3183E-2</v>
+        <v>0.013183</v>
       </c>
       <c r="AG9">
-        <v>1.5136E-2</v>
+        <v>0.015136</v>
       </c>
       <c r="AH9">
-        <v>1.7378000000000001E-2</v>
+        <v>0.017378</v>
       </c>
       <c r="AI9">
-        <v>1.9952999999999999E-2</v>
+        <v>0.019953</v>
       </c>
       <c r="AJ9">
-        <v>2.2908999999999999E-2</v>
+        <v>0.022909</v>
       </c>
       <c r="AK9">
-        <v>2.6303E-2</v>
+        <v>0.026303</v>
       </c>
       <c r="AL9">
-        <v>3.0200000000000001E-2</v>
+        <v>0.0302</v>
       </c>
       <c r="AM9">
-        <v>3.4674000000000003E-2</v>
+        <v>0.034674</v>
       </c>
       <c r="AN9">
-        <v>3.9810999999999999E-2</v>
+        <v>0.039811</v>
       </c>
       <c r="AO9">
-        <v>4.5709E-2</v>
+        <v>0.045709</v>
       </c>
       <c r="AP9">
-        <v>5.2481E-2</v>
+        <v>0.052481</v>
       </c>
       <c r="AQ9">
-        <v>6.0255999999999997E-2</v>
+        <v>0.060256</v>
       </c>
       <c r="AR9">
-        <v>6.9182999999999995E-2</v>
+        <v>0.069183</v>
       </c>
       <c r="AS9">
-        <v>7.9433000000000004E-2</v>
+        <v>0.079433</v>
       </c>
       <c r="AT9">
-        <v>9.1201000000000004E-2</v>
+        <v>0.091201</v>
       </c>
       <c r="AU9">
         <v>0.104713</v>
@@ -2517,97 +2557,97 @@
         <v>0.120226</v>
       </c>
       <c r="AW9">
-        <v>0.13803799999999999</v>
+        <v>0.138038</v>
       </c>
       <c r="AX9">
-        <v>0.15848899999999999</v>
+        <v>0.158489</v>
       </c>
       <c r="AY9">
-        <v>0.18196999999999999</v>
+        <v>0.18197</v>
       </c>
       <c r="AZ9">
         <v>0.20893</v>
       </c>
       <c r="BA9">
-        <v>0.23988300000000001</v>
+        <v>0.239883</v>
       </c>
       <c r="BB9">
-        <v>0.27542299999999997</v>
+        <v>0.275423</v>
       </c>
       <c r="BC9">
-        <v>0.31622800000000001</v>
+        <v>0.316228</v>
       </c>
       <c r="BD9">
-        <v>0.36307800000000001</v>
+        <v>0.363078</v>
       </c>
       <c r="BE9">
-        <v>0.41686899999999999</v>
+        <v>0.416869</v>
       </c>
       <c r="BF9">
         <v>0.47863</v>
       </c>
       <c r="BG9">
-        <v>0.54954099999999995</v>
+        <v>0.549541</v>
       </c>
       <c r="BH9">
-        <v>0.63095699999999999</v>
+        <v>0.630957</v>
       </c>
       <c r="BI9">
-        <v>0.72443599999999997</v>
+        <v>0.724436</v>
       </c>
       <c r="BJ9">
-        <v>0.83176399999999995</v>
+        <v>0.831764</v>
       </c>
       <c r="BK9">
-        <v>0.95499299999999998</v>
+        <v>0.954993</v>
       </c>
       <c r="BL9">
-        <v>1.0964780000000001</v>
+        <v>1.096478</v>
       </c>
       <c r="BM9">
-        <v>1.2589250000000001</v>
+        <v>1.258925</v>
       </c>
       <c r="BN9">
-        <v>1.4454400000000001</v>
+        <v>1.44544</v>
       </c>
       <c r="BO9">
-        <v>1.6595869999999999</v>
+        <v>1.659587</v>
       </c>
       <c r="BP9">
-        <v>1.9054610000000001</v>
+        <v>1.905461</v>
       </c>
       <c r="BQ9">
-        <v>2.1877620000000002</v>
+        <v>2.187762</v>
       </c>
       <c r="BR9">
-        <v>2.5118860000000001</v>
+        <v>2.511886</v>
       </c>
       <c r="BS9">
-        <v>2.8840309999999998</v>
+        <v>2.884031</v>
       </c>
       <c r="BT9">
-        <v>3.3113109999999999</v>
+        <v>3.311311</v>
       </c>
       <c r="BU9">
-        <v>3.8018939999999999</v>
+        <v>3.801894</v>
       </c>
       <c r="BV9">
-        <v>4.3651580000000001</v>
+        <v>4.365158</v>
       </c>
       <c r="BW9">
-        <v>5.0118720000000003</v>
+        <v>5.011872</v>
       </c>
       <c r="BX9">
-        <v>5.7543990000000003</v>
+        <v>5.754399</v>
       </c>
       <c r="BY9">
-        <v>6.6069339999999999</v>
+        <v>6.606934</v>
       </c>
       <c r="BZ9">
-        <v>7.5857760000000001</v>
+        <v>7.585776</v>
       </c>
       <c r="CA9">
-        <v>8.7096359999999997</v>
+        <v>8.709636</v>
       </c>
       <c r="CB9">
         <v>10</v>
@@ -2616,49 +2656,49 @@
         <v>11.481536</v>
       </c>
       <c r="CD9">
-        <v>13.182567000000001</v>
+        <v>13.182567</v>
       </c>
       <c r="CE9">
         <v>15.135612</v>
       </c>
       <c r="CF9">
-        <v>17.378008000000001</v>
+        <v>17.378008</v>
       </c>
       <c r="CG9">
-        <v>19.952622999999999</v>
+        <v>19.952623</v>
       </c>
       <c r="CH9">
-        <v>22.908677000000001</v>
+        <v>22.908677</v>
       </c>
       <c r="CI9">
-        <v>26.302679999999999</v>
+        <v>26.30268</v>
       </c>
       <c r="CJ9">
         <v>30.199517</v>
       </c>
       <c r="CK9">
-        <v>34.673684999999999</v>
+        <v>34.673685</v>
       </c>
       <c r="CL9">
-        <v>39.810716999999997</v>
+        <v>39.810717</v>
       </c>
       <c r="CM9">
-        <v>45.708818999999998</v>
+        <v>45.708819</v>
       </c>
       <c r="CN9">
-        <v>52.480746000000003</v>
+        <v>52.480746</v>
       </c>
       <c r="CO9">
-        <v>60.255958999999997</v>
+        <v>60.255959</v>
       </c>
       <c r="CP9">
-        <v>69.183097000000004</v>
+        <v>69.183097</v>
       </c>
       <c r="CQ9">
-        <v>79.432822999999999</v>
+        <v>79.432823</v>
       </c>
       <c r="CR9">
-        <v>91.201083999999994</v>
+        <v>91.201084</v>
       </c>
       <c r="CS9">
         <v>104.712855</v>
@@ -2667,120 +2707,120 @@
         <v>120.226443</v>
       </c>
       <c r="CU9">
-        <v>138.03842599999999</v>
+        <v>138.038426</v>
       </c>
       <c r="CV9">
-        <v>158.48931899999999</v>
+        <v>158.489319</v>
       </c>
       <c r="CW9">
-        <v>181.97008600000001</v>
+        <v>181.970086</v>
       </c>
       <c r="CX9">
-        <v>208.92961299999999</v>
+        <v>208.929613</v>
       </c>
       <c r="CY9">
-        <v>239.88329200000001</v>
+        <v>239.883292</v>
       </c>
       <c r="CZ9">
-        <v>275.42286999999999</v>
+        <v>275.42287</v>
       </c>
       <c r="DA9">
-        <v>316.22776599999997</v>
+        <v>316.227766</v>
       </c>
       <c r="DB9">
-        <v>363.07805500000001</v>
+        <v>363.078055</v>
       </c>
       <c r="DC9">
-        <v>416.86938300000003</v>
+        <v>416.869383</v>
       </c>
       <c r="DD9">
-        <v>478.63009199999999</v>
+        <v>478.630092</v>
       </c>
       <c r="DE9">
-        <v>549.54087400000003</v>
+        <v>549.540874</v>
       </c>
       <c r="DF9">
-        <v>630.95734400000003</v>
+        <v>630.957344</v>
       </c>
       <c r="DG9">
-        <v>724.43596000000002</v>
+        <v>724.43596</v>
       </c>
       <c r="DH9">
-        <v>831.76377100000002</v>
+        <v>831.763771</v>
       </c>
       <c r="DI9">
-        <v>954.99258599999996</v>
+        <v>954.992586</v>
       </c>
       <c r="DJ9">
         <v>1096.478196</v>
       </c>
       <c r="DK9">
-        <v>1258.9254120000001</v>
+        <v>1258.925412</v>
       </c>
       <c r="DL9">
-        <v>1445.4397710000001</v>
+        <v>1445.439771</v>
       </c>
       <c r="DM9">
-        <v>1659.5869070000001</v>
+        <v>1659.586907</v>
       </c>
       <c r="DN9">
         <v>1905.460718</v>
       </c>
       <c r="DO9">
-        <v>2187.7616240000002</v>
+        <v>2187.761624</v>
       </c>
       <c r="DP9">
-        <v>2511.8864319999998</v>
+        <v>2511.886432</v>
       </c>
       <c r="DQ9">
-        <v>2884.0315030000002</v>
+        <v>2884.031503</v>
       </c>
       <c r="DR9">
-        <v>3311.3112150000002</v>
+        <v>3311.311215</v>
       </c>
       <c r="DS9">
         <v>3801.893963</v>
       </c>
       <c r="DT9">
-        <v>4365.1583220000002</v>
+        <v>4365.158322</v>
       </c>
       <c r="DU9">
-        <v>5011.8723360000004</v>
+        <v>5011.872336</v>
       </c>
       <c r="DV9">
-        <v>5754.3993730000002</v>
+        <v>5754.399373</v>
       </c>
       <c r="DW9">
-        <v>6606.9344799999999</v>
+        <v>6606.93448</v>
       </c>
       <c r="DX9">
-        <v>7585.7757499999998</v>
+        <v>7585.77575</v>
       </c>
       <c r="DY9">
-        <v>8709.6358999999993</v>
+        <v>8709.6359</v>
       </c>
       <c r="DZ9">
         <v>10000</v>
       </c>
     </row>
-    <row r="10" spans="1:131" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>31</v>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
         <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G10" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="H10" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="I10">
         <v>1.5</v>
@@ -2816,16 +2856,16 @@
         <v>1.518</v>
       </c>
       <c r="T10">
-        <v>1.35E-2</v>
+        <v>0.0135</v>
       </c>
       <c r="U10">
-        <v>7.6070000000000002</v>
+        <v>7.607</v>
       </c>
       <c r="V10" t="s">
         <v>41</v>
       </c>
       <c r="W10">
-        <v>77.200999999999993</v>
+        <v>77.201</v>
       </c>
       <c r="X10">
         <v>2.54</v>
@@ -2834,13 +2874,13 @@
         <v>0.877</v>
       </c>
       <c r="Z10">
-        <v>6.8410000000000002</v>
+        <v>6.841</v>
       </c>
       <c r="AA10">
         <v>2.806</v>
       </c>
       <c r="AB10">
-        <v>26.242999999999999</v>
+        <v>26.243</v>
       </c>
       <c r="AC10">
         <v>202.429</v>
@@ -2918,115 +2958,115 @@
         <v>0</v>
       </c>
       <c r="BC10">
-        <v>9.6069999999999992E-3</v>
+        <v>0.009607</v>
       </c>
       <c r="BD10">
-        <v>8.6626999999999996E-2</v>
+        <v>0.086627</v>
       </c>
       <c r="BE10">
         <v>0.21017</v>
       </c>
       <c r="BF10">
-        <v>0.30978800000000001</v>
+        <v>0.309788</v>
       </c>
       <c r="BG10">
-        <v>0.39233299999999999</v>
+        <v>0.392333</v>
       </c>
       <c r="BH10">
-        <v>0.45777000000000001</v>
+        <v>0.45777</v>
       </c>
       <c r="BI10">
-        <v>0.50451299999999999</v>
+        <v>0.504513</v>
       </c>
       <c r="BJ10">
-        <v>0.54165200000000002</v>
+        <v>0.541652</v>
       </c>
       <c r="BK10">
-        <v>0.57593300000000003</v>
+        <v>0.575933</v>
       </c>
       <c r="BL10">
-        <v>0.61725300000000005</v>
+        <v>0.617253</v>
       </c>
       <c r="BM10">
-        <v>0.67142599999999997</v>
+        <v>0.671426</v>
       </c>
       <c r="BN10">
         <v>0.742537</v>
       </c>
       <c r="BO10">
-        <v>0.82822499999999999</v>
+        <v>0.828225</v>
       </c>
       <c r="BP10">
-        <v>0.92471499999999995</v>
+        <v>0.924715</v>
       </c>
       <c r="BQ10">
-        <v>1.0254049999999999</v>
+        <v>1.025405</v>
       </c>
       <c r="BR10">
         <v>1.12639</v>
       </c>
       <c r="BS10">
-        <v>1.2253620000000001</v>
+        <v>1.225362</v>
       </c>
       <c r="BT10">
-        <v>1.3219069999999999</v>
+        <v>1.321907</v>
       </c>
       <c r="BU10">
         <v>1.417646</v>
       </c>
       <c r="BV10">
-        <v>1.5147930000000001</v>
+        <v>1.514793</v>
       </c>
       <c r="BW10">
         <v>1.618986</v>
       </c>
       <c r="BX10">
-        <v>1.7347349999999999</v>
+        <v>1.734735</v>
       </c>
       <c r="BY10">
-        <v>1.8709849999999999</v>
+        <v>1.870985</v>
       </c>
       <c r="BZ10">
         <v>2.031158</v>
       </c>
       <c r="CA10">
-        <v>2.2231719999999999</v>
+        <v>2.223172</v>
       </c>
       <c r="CB10">
         <v>2.441789</v>
       </c>
       <c r="CC10">
-        <v>2.6885789999999998</v>
+        <v>2.688579</v>
       </c>
       <c r="CD10">
-        <v>2.9455870000000002</v>
+        <v>2.945587</v>
       </c>
       <c r="CE10">
-        <v>3.2056249999999999</v>
+        <v>3.205625</v>
       </c>
       <c r="CF10">
-        <v>3.4446509999999999</v>
+        <v>3.444651</v>
       </c>
       <c r="CG10">
-        <v>3.6509809999999998</v>
+        <v>3.650981</v>
       </c>
       <c r="CH10">
-        <v>3.8053650000000001</v>
+        <v>3.805365</v>
       </c>
       <c r="CI10">
-        <v>3.8992399999999998</v>
+        <v>3.89924</v>
       </c>
       <c r="CJ10">
-        <v>3.9248940000000001</v>
+        <v>3.924894</v>
       </c>
       <c r="CK10">
-        <v>3.8816660000000001</v>
+        <v>3.881666</v>
       </c>
       <c r="CL10">
-        <v>3.7738809999999998</v>
+        <v>3.773881</v>
       </c>
       <c r="CM10">
-        <v>3.6103239999999999</v>
+        <v>3.610324</v>
       </c>
       <c r="CN10">
         <v>3.403762</v>
@@ -3041,13 +3081,13 @@
         <v>2.669991</v>
       </c>
       <c r="CR10">
-        <v>2.4287939999999999</v>
+        <v>2.428794</v>
       </c>
       <c r="CS10">
-        <v>2.2053430000000001</v>
+        <v>2.205343</v>
       </c>
       <c r="CT10">
-        <v>1.9973320000000001</v>
+        <v>1.997332</v>
       </c>
       <c r="CU10">
         <v>1.80813</v>
@@ -3059,7 +3099,7 @@
         <v>1.473393</v>
       </c>
       <c r="CX10">
-        <v>1.3307580000000001</v>
+        <v>1.330758</v>
       </c>
       <c r="CY10">
         <v>1.21201</v>
@@ -3071,28 +3111,28 @@
         <v>1.040246</v>
       </c>
       <c r="DB10">
-        <v>0.98264799999999997</v>
+        <v>0.982648</v>
       </c>
       <c r="DC10">
-        <v>0.93732800000000005</v>
+        <v>0.937328</v>
       </c>
       <c r="DD10">
-        <v>0.89641599999999999</v>
+        <v>0.896416</v>
       </c>
       <c r="DE10">
-        <v>0.85302500000000003</v>
+        <v>0.853025</v>
       </c>
       <c r="DF10">
-        <v>0.79914499999999999</v>
+        <v>0.799145</v>
       </c>
       <c r="DG10">
-        <v>0.73419999999999996</v>
+        <v>0.7342</v>
       </c>
       <c r="DH10">
         <v>0.646733</v>
       </c>
       <c r="DI10">
-        <v>0.49036299999999999</v>
+        <v>0.490363</v>
       </c>
       <c r="DJ10">
         <v>0</v>
@@ -3146,24 +3186,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:131" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>31</v>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
         <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G11" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="H11" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="I11">
         <v>1.5</v>
@@ -3196,19 +3236,19 @@
         <v>14.24</v>
       </c>
       <c r="S11">
-        <v>1.5109999999999999</v>
+        <v>1.511</v>
       </c>
       <c r="T11">
-        <v>1.35E-2</v>
+        <v>0.0135</v>
       </c>
       <c r="U11">
-        <v>7.7930000000000001</v>
+        <v>7.793</v>
       </c>
       <c r="V11" t="s">
         <v>41</v>
       </c>
       <c r="W11">
-        <v>78.221999999999994</v>
+        <v>78.222</v>
       </c>
       <c r="X11">
         <v>2.57</v>
@@ -3217,16 +3257,16 @@
         <v>0.871</v>
       </c>
       <c r="Z11">
-        <v>6.8879999999999999</v>
+        <v>6.888</v>
       </c>
       <c r="AA11">
-        <v>2.8340000000000001</v>
+        <v>2.834</v>
       </c>
       <c r="AB11">
-        <v>26.283000000000001</v>
+        <v>26.283</v>
       </c>
       <c r="AC11">
-        <v>207.65700000000001</v>
+        <v>207.657</v>
       </c>
       <c r="AE11">
         <v>0</v>
@@ -3301,46 +3341,46 @@
         <v>0</v>
       </c>
       <c r="BC11">
-        <v>9.4090000000000007E-3</v>
+        <v>0.009409</v>
       </c>
       <c r="BD11">
-        <v>8.4961999999999996E-2</v>
+        <v>0.084962</v>
       </c>
       <c r="BE11">
         <v>0.207399</v>
       </c>
       <c r="BF11">
-        <v>0.30606499999999998</v>
+        <v>0.306065</v>
       </c>
       <c r="BG11">
         <v>0.387824</v>
       </c>
       <c r="BH11">
-        <v>0.45264799999999999</v>
+        <v>0.452648</v>
       </c>
       <c r="BI11">
-        <v>0.49897799999999998</v>
+        <v>0.498978</v>
       </c>
       <c r="BJ11">
-        <v>0.53584299999999996</v>
+        <v>0.535843</v>
       </c>
       <c r="BK11">
-        <v>0.56994599999999995</v>
+        <v>0.569946</v>
       </c>
       <c r="BL11">
         <v>0.61112</v>
       </c>
       <c r="BM11">
-        <v>0.66513800000000001</v>
+        <v>0.665138</v>
       </c>
       <c r="BN11">
-        <v>0.73606499999999997</v>
+        <v>0.736065</v>
       </c>
       <c r="BO11">
-        <v>0.82155299999999998</v>
+        <v>0.821553</v>
       </c>
       <c r="BP11">
-        <v>0.91786199999999996</v>
+        <v>0.917862</v>
       </c>
       <c r="BQ11">
         <v>1.018427</v>
@@ -3355,7 +3395,7 @@
         <v>1.315129</v>
       </c>
       <c r="BU11">
-        <v>1.4111940000000001</v>
+        <v>1.411194</v>
       </c>
       <c r="BV11">
         <v>1.508848</v>
@@ -3373,10 +3413,10 @@
         <v>2.030211</v>
       </c>
       <c r="CA11">
-        <v>2.2243940000000002</v>
+        <v>2.224394</v>
       </c>
       <c r="CB11">
-        <v>2.4454199999999999</v>
+        <v>2.44542</v>
       </c>
       <c r="CC11">
         <v>2.694782</v>
@@ -3385,7 +3425,7 @@
         <v>2.954243</v>
       </c>
       <c r="CE11">
-        <v>3.2164259999999998</v>
+        <v>3.216426</v>
       </c>
       <c r="CF11">
         <v>3.456931</v>
@@ -3394,46 +3434,46 @@
         <v>3.66378</v>
       </c>
       <c r="CH11">
-        <v>3.8173810000000001</v>
+        <v>3.817381</v>
       </c>
       <c r="CI11">
         <v>3.908881</v>
       </c>
       <c r="CJ11">
-        <v>3.9304709999999998</v>
+        <v>3.930471</v>
       </c>
       <c r="CK11">
-        <v>3.8816419999999998</v>
+        <v>3.881642</v>
       </c>
       <c r="CL11">
-        <v>3.7674089999999998</v>
+        <v>3.767409</v>
       </c>
       <c r="CM11">
-        <v>3.5975730000000001</v>
+        <v>3.597573</v>
       </c>
       <c r="CN11">
-        <v>3.3860070000000002</v>
+        <v>3.386007</v>
       </c>
       <c r="CO11">
-        <v>3.1481979999999998</v>
+        <v>3.148198</v>
       </c>
       <c r="CP11">
-        <v>2.8978169999999999</v>
+        <v>2.897817</v>
       </c>
       <c r="CQ11">
-        <v>2.6499250000000001</v>
+        <v>2.649925</v>
       </c>
       <c r="CR11">
-        <v>2.4112830000000001</v>
+        <v>2.411283</v>
       </c>
       <c r="CS11">
         <v>2.190652</v>
       </c>
       <c r="CT11">
-        <v>1.9847969999999999</v>
+        <v>1.984797</v>
       </c>
       <c r="CU11">
-        <v>1.7963229999999999</v>
+        <v>1.796323</v>
       </c>
       <c r="CV11">
         <v>1.619062</v>
@@ -3445,34 +3485,34 @@
         <v>1.314241</v>
       </c>
       <c r="CY11">
-        <v>1.1963250000000001</v>
+        <v>1.196325</v>
       </c>
       <c r="CZ11">
-        <v>1.1050899999999999</v>
+        <v>1.10509</v>
       </c>
       <c r="DA11">
         <v>1.042875</v>
       </c>
       <c r="DB11">
-        <v>1.0036560000000001</v>
+        <v>1.003656</v>
       </c>
       <c r="DC11">
-        <v>0.97883900000000001</v>
+        <v>0.978839</v>
       </c>
       <c r="DD11">
-        <v>0.95471300000000003</v>
+        <v>0.954713</v>
       </c>
       <c r="DE11">
-        <v>0.91742800000000002</v>
+        <v>0.917428</v>
       </c>
       <c r="DF11">
-        <v>0.85471799999999998</v>
+        <v>0.854718</v>
       </c>
       <c r="DG11">
-        <v>0.76769500000000002</v>
+        <v>0.767695</v>
       </c>
       <c r="DH11">
-        <v>0.65036700000000003</v>
+        <v>0.650367</v>
       </c>
       <c r="DI11">
         <v>0.472995</v>
@@ -3529,24 +3569,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:131" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>31</v>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E12" t="s">
         <v>33</v>
       </c>
       <c r="F12" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="G12" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H12" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="I12">
         <v>1.5</v>
@@ -3582,28 +3622,28 @@
         <v>1.496</v>
       </c>
       <c r="T12">
-        <v>1.3599999999999999E-2</v>
+        <v>0.0136</v>
       </c>
       <c r="U12">
-        <v>7.7930000000000001</v>
+        <v>7.793</v>
       </c>
       <c r="V12" t="s">
         <v>41</v>
       </c>
       <c r="W12">
-        <v>79.841999999999999</v>
+        <v>79.842</v>
       </c>
       <c r="X12">
         <v>2.59</v>
       </c>
       <c r="Y12">
-        <v>0.85899999999999999</v>
+        <v>0.859</v>
       </c>
       <c r="Z12">
-        <v>6.9820000000000002</v>
+        <v>6.982</v>
       </c>
       <c r="AA12">
-        <v>2.8820000000000001</v>
+        <v>2.882</v>
       </c>
       <c r="AB12">
         <v>26.727</v>
@@ -3684,46 +3724,46 @@
         <v>0</v>
       </c>
       <c r="BC12">
-        <v>9.162E-3</v>
+        <v>0.009162</v>
       </c>
       <c r="BD12">
-        <v>8.2834000000000005E-2</v>
+        <v>0.082834</v>
       </c>
       <c r="BE12">
         <v>0.203157</v>
       </c>
       <c r="BF12">
-        <v>0.30008899999999999</v>
+        <v>0.300089</v>
       </c>
       <c r="BG12">
-        <v>0.38043500000000002</v>
+        <v>0.380435</v>
       </c>
       <c r="BH12">
         <v>0.444191</v>
       </c>
       <c r="BI12">
-        <v>0.48984299999999997</v>
+        <v>0.489843</v>
       </c>
       <c r="BJ12">
-        <v>0.52629599999999999</v>
+        <v>0.526296</v>
       </c>
       <c r="BK12">
-        <v>0.56015099999999995</v>
+        <v>0.560151</v>
       </c>
       <c r="BL12">
-        <v>0.60109000000000001</v>
+        <v>0.60109</v>
       </c>
       <c r="BM12">
-        <v>0.65477300000000005</v>
+        <v>0.654773</v>
       </c>
       <c r="BN12">
-        <v>0.72518800000000005</v>
+        <v>0.725188</v>
       </c>
       <c r="BO12">
-        <v>0.80999100000000002</v>
+        <v>0.809991</v>
       </c>
       <c r="BP12">
-        <v>0.90548499999999998</v>
+        <v>0.905485</v>
       </c>
       <c r="BQ12">
         <v>1.005204</v>
@@ -3735,130 +3775,130 @@
         <v>1.203705</v>
       </c>
       <c r="BT12">
-        <v>1.2998940000000001</v>
+        <v>1.299894</v>
       </c>
       <c r="BU12">
-        <v>1.3955379999999999</v>
+        <v>1.395538</v>
       </c>
       <c r="BV12">
-        <v>1.4928170000000001</v>
+        <v>1.492817</v>
       </c>
       <c r="BW12">
-        <v>1.5973360000000001</v>
+        <v>1.597336</v>
       </c>
       <c r="BX12">
-        <v>1.7135830000000001</v>
+        <v>1.713583</v>
       </c>
       <c r="BY12">
         <v>1.850525</v>
       </c>
       <c r="BZ12">
-        <v>2.0115820000000002</v>
+        <v>2.011582</v>
       </c>
       <c r="CA12">
-        <v>2.2046999999999999</v>
+        <v>2.2047</v>
       </c>
       <c r="CB12">
-        <v>2.4245969999999999</v>
+        <v>2.424597</v>
       </c>
       <c r="CC12">
-        <v>2.6728540000000001</v>
+        <v>2.672854</v>
       </c>
       <c r="CD12">
-        <v>2.9313980000000002</v>
+        <v>2.931398</v>
       </c>
       <c r="CE12">
-        <v>3.1929319999999999</v>
+        <v>3.192932</v>
       </c>
       <c r="CF12">
-        <v>3.4331100000000001</v>
+        <v>3.43311</v>
       </c>
       <c r="CG12">
         <v>3.639907</v>
       </c>
       <c r="CH12">
-        <v>3.7936480000000001</v>
+        <v>3.793648</v>
       </c>
       <c r="CI12">
-        <v>3.8853979999999999</v>
+        <v>3.885398</v>
       </c>
       <c r="CJ12">
         <v>3.907305</v>
       </c>
       <c r="CK12">
-        <v>3.8589090000000001</v>
+        <v>3.858909</v>
       </c>
       <c r="CL12">
-        <v>3.7454040000000002</v>
+        <v>3.745404</v>
       </c>
       <c r="CM12">
-        <v>3.5769639999999998</v>
+        <v>3.576964</v>
       </c>
       <c r="CN12">
-        <v>3.3680970000000001</v>
+        <v>3.368097</v>
       </c>
       <c r="CO12">
-        <v>3.1351369999999998</v>
+        <v>3.135137</v>
       </c>
       <c r="CP12">
         <v>2.892658</v>
       </c>
       <c r="CQ12">
-        <v>2.6562229999999998</v>
+        <v>2.656223</v>
       </c>
       <c r="CR12">
-        <v>2.4326159999999999</v>
+        <v>2.432616</v>
       </c>
       <c r="CS12">
-        <v>2.2293020000000001</v>
+        <v>2.229302</v>
       </c>
       <c r="CT12">
-        <v>2.0413649999999999</v>
+        <v>2.041365</v>
       </c>
       <c r="CU12">
-        <v>1.8684179999999999</v>
+        <v>1.868418</v>
       </c>
       <c r="CV12">
-        <v>1.7017439999999999</v>
+        <v>1.701744</v>
       </c>
       <c r="CW12">
         <v>1.544017</v>
       </c>
       <c r="CX12">
-        <v>1.3925909999999999</v>
+        <v>1.392591</v>
       </c>
       <c r="CY12">
-        <v>1.2578039999999999</v>
+        <v>1.257804</v>
       </c>
       <c r="CZ12">
-        <v>1.1414420000000001</v>
+        <v>1.141442</v>
       </c>
       <c r="DA12">
-        <v>1.0510569999999999</v>
+        <v>1.051057</v>
       </c>
       <c r="DB12">
-        <v>0.98645000000000005</v>
+        <v>0.98645</v>
       </c>
       <c r="DC12">
-        <v>0.94575299999999995</v>
+        <v>0.945753</v>
       </c>
       <c r="DD12">
         <v>0.919234</v>
       </c>
       <c r="DE12">
-        <v>0.89427000000000001</v>
+        <v>0.89427</v>
       </c>
       <c r="DF12">
-        <v>0.85628599999999999</v>
+        <v>0.856286</v>
       </c>
       <c r="DG12">
         <v>0.79996</v>
       </c>
       <c r="DH12">
-        <v>0.71068900000000002</v>
+        <v>0.710689</v>
       </c>
       <c r="DI12">
-        <v>0.53953700000000004</v>
+        <v>0.539537</v>
       </c>
       <c r="DJ12">
         <v>0</v>
@@ -3912,248 +3952,248 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:131" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>62</v>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="BC13">
-        <f t="shared" ref="BC13" si="2">AVERAGE(BC10:BC12)</f>
-        <v>9.3926666666666655E-3</v>
+        <f t="shared" si="1" ref="BC13:DI20">AVERAGE(BC10:BC12)</f>
+        <v>0.009392666666666665</v>
       </c>
       <c r="BD13">
-        <f t="shared" ref="BD13" si="3">AVERAGE(BD10:BD12)</f>
-        <v>8.480766666666667E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.08480766666666667</v>
       </c>
       <c r="BE13">
-        <f t="shared" ref="BE13" si="4">AVERAGE(BE10:BE12)</f>
+        <f t="shared" si="1"/>
         <v>0.20690866666666666</v>
       </c>
       <c r="BF13">
-        <f t="shared" ref="BF13" si="5">AVERAGE(BF10:BF12)</f>
+        <f t="shared" si="1"/>
         <v>0.30531400000000003</v>
       </c>
       <c r="BG13">
-        <f t="shared" ref="BG13" si="6">AVERAGE(BG10:BG12)</f>
+        <f t="shared" si="1"/>
         <v>0.38686400000000004</v>
       </c>
       <c r="BH13">
-        <f t="shared" ref="BH13" si="7">AVERAGE(BH10:BH12)</f>
-        <v>0.45153633333333332</v>
+        <f t="shared" si="1"/>
+        <v>0.4515363333333333</v>
       </c>
       <c r="BI13">
-        <f t="shared" ref="BI13" si="8">AVERAGE(BI10:BI12)</f>
+        <f t="shared" si="1"/>
         <v>0.497778</v>
       </c>
       <c r="BJ13">
-        <f t="shared" ref="BJ13" si="9">AVERAGE(BJ10:BJ12)</f>
-        <v>0.53459699999999988</v>
+        <f t="shared" si="1"/>
+        <v>0.5345969999999999</v>
       </c>
       <c r="BK13">
-        <f t="shared" ref="BK13" si="10">AVERAGE(BK10:BK12)</f>
-        <v>0.56867666666666661</v>
+        <f t="shared" si="1"/>
+        <v>0.5686766666666666</v>
       </c>
       <c r="BL13">
-        <f t="shared" ref="BL13" si="11">AVERAGE(BL10:BL12)</f>
-        <v>0.60982100000000006</v>
+        <f t="shared" si="1"/>
+        <v>0.6098210000000001</v>
       </c>
       <c r="BM13">
-        <f t="shared" ref="BM13" si="12">AVERAGE(BM10:BM12)</f>
-        <v>0.66377900000000001</v>
+        <f t="shared" si="1"/>
+        <v>0.663779</v>
       </c>
       <c r="BN13">
-        <f t="shared" ref="BN13" si="13">AVERAGE(BN10:BN12)</f>
-        <v>0.73459666666666668</v>
+        <f t="shared" si="1"/>
+        <v>0.7345966666666667</v>
       </c>
       <c r="BO13">
-        <f t="shared" ref="BO13" si="14">AVERAGE(BO10:BO12)</f>
-        <v>0.81992300000000007</v>
+        <f t="shared" si="1"/>
+        <v>0.8199230000000001</v>
       </c>
       <c r="BP13">
-        <f t="shared" ref="BP13" si="15">AVERAGE(BP10:BP12)</f>
-        <v>0.91602066666666671</v>
+        <f t="shared" si="1"/>
+        <v>0.9160206666666667</v>
       </c>
       <c r="BQ13">
-        <f t="shared" ref="BQ13" si="16">AVERAGE(BQ10:BQ12)</f>
+        <f t="shared" si="1"/>
         <v>1.0163453333333334</v>
       </c>
       <c r="BR13">
-        <f t="shared" ref="BR13" si="17">AVERAGE(BR10:BR12)</f>
+        <f t="shared" si="1"/>
         <v>1.1170383333333334</v>
       </c>
       <c r="BS13">
-        <f t="shared" ref="BS13" si="18">AVERAGE(BS10:BS12)</f>
+        <f t="shared" si="1"/>
         <v>1.2158236666666669</v>
       </c>
       <c r="BT13">
-        <f t="shared" ref="BT13" si="19">AVERAGE(BT10:BT12)</f>
-        <v>1.3123100000000001</v>
+        <f t="shared" si="1"/>
+        <v>1.31231</v>
       </c>
       <c r="BU13">
-        <f t="shared" ref="BU13" si="20">AVERAGE(BU10:BU12)</f>
+        <f t="shared" si="1"/>
         <v>1.408126</v>
       </c>
       <c r="BV13">
-        <f t="shared" ref="BV13" si="21">AVERAGE(BV10:BV12)</f>
-        <v>1.5054860000000001</v>
+        <f t="shared" si="1"/>
+        <v>1.505486</v>
       </c>
       <c r="BW13">
-        <f t="shared" ref="BW13" si="22">AVERAGE(BW10:BW12)</f>
+        <f t="shared" si="1"/>
         <v>1.6100383333333335</v>
       </c>
       <c r="BX13">
-        <f t="shared" ref="BX13" si="23">AVERAGE(BX10:BX12)</f>
+        <f t="shared" si="1"/>
         <v>1.7263019999999998</v>
       </c>
       <c r="BY13">
-        <f t="shared" ref="BY13" si="24">AVERAGE(BY10:BY12)</f>
+        <f t="shared" si="1"/>
         <v>1.8632549999999999</v>
       </c>
       <c r="BZ13">
-        <f t="shared" ref="BZ13" si="25">AVERAGE(BZ10:BZ12)</f>
-        <v>2.0243169999999999</v>
+        <f t="shared" si="1"/>
+        <v>2.024317</v>
       </c>
       <c r="CA13">
-        <f t="shared" ref="CA13" si="26">AVERAGE(CA10:CA12)</f>
+        <f t="shared" si="1"/>
         <v>2.217422</v>
       </c>
       <c r="CB13">
-        <f t="shared" ref="CB13" si="27">AVERAGE(CB10:CB12)</f>
+        <f t="shared" si="1"/>
         <v>2.4372686666666667</v>
       </c>
       <c r="CC13">
-        <f t="shared" ref="CC13" si="28">AVERAGE(CC10:CC12)</f>
-        <v>2.6854049999999998</v>
+        <f t="shared" si="1"/>
+        <v>2.685405</v>
       </c>
       <c r="CD13">
-        <f t="shared" ref="CD13" si="29">AVERAGE(CD10:CD12)</f>
+        <f t="shared" si="1"/>
         <v>2.9437426666666666</v>
       </c>
       <c r="CE13">
-        <f t="shared" ref="CE13" si="30">AVERAGE(CE10:CE12)</f>
-        <v>3.2049943333333331</v>
+        <f t="shared" si="1"/>
+        <v>3.204994333333333</v>
       </c>
       <c r="CF13">
-        <f t="shared" ref="CF13" si="31">AVERAGE(CF10:CF12)</f>
+        <f t="shared" si="1"/>
         <v>3.4448973333333335</v>
       </c>
       <c r="CG13">
-        <f t="shared" ref="CG13" si="32">AVERAGE(CG10:CG12)</f>
-        <v>3.6515559999999998</v>
+        <f t="shared" si="1"/>
+        <v>3.651556</v>
       </c>
       <c r="CH13">
-        <f t="shared" ref="CH13" si="33">AVERAGE(CH10:CH12)</f>
-        <v>3.8054646666666669</v>
+        <f t="shared" si="1"/>
+        <v>3.805464666666667</v>
       </c>
       <c r="CI13">
-        <f t="shared" ref="CI13" si="34">AVERAGE(CI10:CI12)</f>
+        <f t="shared" si="1"/>
         <v>3.8978396666666666</v>
       </c>
       <c r="CJ13">
-        <f t="shared" ref="CJ13" si="35">AVERAGE(CJ10:CJ12)</f>
+        <f t="shared" si="1"/>
         <v>3.92089</v>
       </c>
       <c r="CK13">
-        <f t="shared" ref="CK13" si="36">AVERAGE(CK10:CK12)</f>
-        <v>3.8740723333333338</v>
+        <f t="shared" si="1"/>
+        <v>3.874072333333334</v>
       </c>
       <c r="CL13">
-        <f t="shared" ref="CL13" si="37">AVERAGE(CL10:CL12)</f>
+        <f t="shared" si="1"/>
         <v>3.7622313333333337</v>
       </c>
       <c r="CM13">
-        <f t="shared" ref="CM13" si="38">AVERAGE(CM10:CM12)</f>
+        <f t="shared" si="1"/>
         <v>3.5949536666666666</v>
       </c>
       <c r="CN13">
-        <f t="shared" ref="CN13" si="39">AVERAGE(CN10:CN12)</f>
+        <f t="shared" si="1"/>
         <v>3.3859553333333334</v>
       </c>
       <c r="CO13">
-        <f t="shared" ref="CO13" si="40">AVERAGE(CO10:CO12)</f>
-        <v>3.1507453333333331</v>
+        <f t="shared" si="1"/>
+        <v>3.150745333333333</v>
       </c>
       <c r="CP13">
-        <f t="shared" ref="CP13" si="41">AVERAGE(CP10:CP12)</f>
+        <f t="shared" si="1"/>
         <v>2.9032196666666663</v>
       </c>
       <c r="CQ13">
-        <f t="shared" ref="CQ13" si="42">AVERAGE(CQ10:CQ12)</f>
-        <v>2.6587130000000001</v>
+        <f t="shared" si="1"/>
+        <v>2.658713</v>
       </c>
       <c r="CR13">
-        <f t="shared" ref="CR13" si="43">AVERAGE(CR10:CR12)</f>
+        <f t="shared" si="1"/>
         <v>2.4242310000000002</v>
       </c>
       <c r="CS13">
-        <f t="shared" ref="CS13" si="44">AVERAGE(CS10:CS12)</f>
-        <v>2.2084323333333331</v>
+        <f t="shared" si="1"/>
+        <v>2.208432333333333</v>
       </c>
       <c r="CT13">
-        <f t="shared" ref="CT13" si="45">AVERAGE(CT10:CT12)</f>
+        <f t="shared" si="1"/>
         <v>2.0078313333333333</v>
       </c>
       <c r="CU13">
-        <f t="shared" ref="CU13" si="46">AVERAGE(CU10:CU12)</f>
+        <f t="shared" si="1"/>
         <v>1.8242903333333331</v>
       </c>
       <c r="CV13">
-        <f t="shared" ref="CV13" si="47">AVERAGE(CV10:CV12)</f>
+        <f t="shared" si="1"/>
         <v>1.6508646666666664</v>
       </c>
       <c r="CW13">
-        <f t="shared" ref="CW13" si="48">AVERAGE(CW10:CW12)</f>
+        <f t="shared" si="1"/>
         <v>1.492013</v>
       </c>
       <c r="CX13">
-        <f t="shared" ref="CX13" si="49">AVERAGE(CX10:CX12)</f>
+        <f t="shared" si="1"/>
         <v>1.3458633333333332</v>
       </c>
       <c r="CY13">
-        <f t="shared" ref="CY13" si="50">AVERAGE(CY10:CY12)</f>
+        <f t="shared" si="1"/>
         <v>1.2220463333333333</v>
       </c>
       <c r="CZ13">
-        <f t="shared" ref="CZ13" si="51">AVERAGE(CZ10:CZ12)</f>
+        <f t="shared" si="1"/>
         <v>1.1204576666666666</v>
       </c>
       <c r="DA13">
-        <f t="shared" ref="DA13" si="52">AVERAGE(DA10:DA12)</f>
+        <f t="shared" si="1"/>
         <v>1.044726</v>
       </c>
       <c r="DB13">
-        <f t="shared" ref="DB13" si="53">AVERAGE(DB10:DB12)</f>
-        <v>0.99091800000000008</v>
+        <f t="shared" si="1"/>
+        <v>0.9909180000000001</v>
       </c>
       <c r="DC13">
-        <f t="shared" ref="DC13" si="54">AVERAGE(DC10:DC12)</f>
-        <v>0.95397333333333334</v>
+        <f t="shared" si="1"/>
+        <v>0.9539733333333333</v>
       </c>
       <c r="DD13">
-        <f t="shared" ref="DD13" si="55">AVERAGE(DD10:DD12)</f>
-        <v>0.92345433333333338</v>
+        <f t="shared" si="1"/>
+        <v>0.9234543333333334</v>
       </c>
       <c r="DE13">
-        <f t="shared" ref="DE13" si="56">AVERAGE(DE10:DE12)</f>
-        <v>0.88824099999999995</v>
+        <f t="shared" si="1"/>
+        <v>0.888241</v>
       </c>
       <c r="DF13">
-        <f t="shared" ref="DF13" si="57">AVERAGE(DF10:DF12)</f>
-        <v>0.83671633333333328</v>
+        <f t="shared" si="1"/>
+        <v>0.8367163333333333</v>
       </c>
       <c r="DG13">
-        <f t="shared" ref="DG13" si="58">AVERAGE(DG10:DG12)</f>
-        <v>0.76728499999999988</v>
+        <f t="shared" si="1"/>
+        <v>0.7672849999999999</v>
       </c>
       <c r="DH13">
-        <f t="shared" ref="DH13" si="59">AVERAGE(DH10:DH12)</f>
-        <v>0.66926299999999994</v>
+        <f t="shared" si="1"/>
+        <v>0.6692629999999999</v>
       </c>
       <c r="DI13">
-        <f t="shared" ref="DI13" si="60">AVERAGE(DI10:DI12)</f>
-        <v>0.50096499999999999</v>
+        <f t="shared" si="1"/>
+        <v>0.500965</v>
       </c>
     </row>
-    <row r="15" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="15" ht="15" customHeight="1">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -4248,57 +4288,57 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:131" x14ac:dyDescent="0.2">
+    <row r="16" ht="15" customHeight="1">
       <c r="AD16">
         <v>0.01</v>
       </c>
       <c r="AE16">
-        <v>1.1481999999999999E-2</v>
+        <v>0.011482</v>
       </c>
       <c r="AF16">
-        <v>1.3183E-2</v>
+        <v>0.013183</v>
       </c>
       <c r="AG16">
-        <v>1.5136E-2</v>
+        <v>0.015136</v>
       </c>
       <c r="AH16">
-        <v>1.7378000000000001E-2</v>
+        <v>0.017378</v>
       </c>
       <c r="AI16">
-        <v>1.9952999999999999E-2</v>
+        <v>0.019953</v>
       </c>
       <c r="AJ16">
-        <v>2.2908999999999999E-2</v>
+        <v>0.022909</v>
       </c>
       <c r="AK16">
-        <v>2.6303E-2</v>
+        <v>0.026303</v>
       </c>
       <c r="AL16">
-        <v>3.0200000000000001E-2</v>
+        <v>0.0302</v>
       </c>
       <c r="AM16">
-        <v>3.4674000000000003E-2</v>
+        <v>0.034674</v>
       </c>
       <c r="AN16">
-        <v>3.9810999999999999E-2</v>
+        <v>0.039811</v>
       </c>
       <c r="AO16">
-        <v>4.5709E-2</v>
+        <v>0.045709</v>
       </c>
       <c r="AP16">
-        <v>5.2481E-2</v>
+        <v>0.052481</v>
       </c>
       <c r="AQ16">
-        <v>6.0255999999999997E-2</v>
+        <v>0.060256</v>
       </c>
       <c r="AR16">
-        <v>6.9182999999999995E-2</v>
+        <v>0.069183</v>
       </c>
       <c r="AS16">
-        <v>7.9433000000000004E-2</v>
+        <v>0.079433</v>
       </c>
       <c r="AT16">
-        <v>9.1201000000000004E-2</v>
+        <v>0.091201</v>
       </c>
       <c r="AU16">
         <v>0.104713</v>
@@ -4307,97 +4347,97 @@
         <v>0.120226</v>
       </c>
       <c r="AW16">
-        <v>0.13803799999999999</v>
+        <v>0.138038</v>
       </c>
       <c r="AX16">
-        <v>0.15848899999999999</v>
+        <v>0.158489</v>
       </c>
       <c r="AY16">
-        <v>0.18196999999999999</v>
+        <v>0.18197</v>
       </c>
       <c r="AZ16">
         <v>0.20893</v>
       </c>
       <c r="BA16">
-        <v>0.23988300000000001</v>
+        <v>0.239883</v>
       </c>
       <c r="BB16">
-        <v>0.27542299999999997</v>
+        <v>0.275423</v>
       </c>
       <c r="BC16">
-        <v>0.31622800000000001</v>
+        <v>0.316228</v>
       </c>
       <c r="BD16">
-        <v>0.36307800000000001</v>
+        <v>0.363078</v>
       </c>
       <c r="BE16">
-        <v>0.41686899999999999</v>
+        <v>0.416869</v>
       </c>
       <c r="BF16">
         <v>0.47863</v>
       </c>
       <c r="BG16">
-        <v>0.54954099999999995</v>
+        <v>0.549541</v>
       </c>
       <c r="BH16">
-        <v>0.63095699999999999</v>
+        <v>0.630957</v>
       </c>
       <c r="BI16">
-        <v>0.72443599999999997</v>
+        <v>0.724436</v>
       </c>
       <c r="BJ16">
-        <v>0.83176399999999995</v>
+        <v>0.831764</v>
       </c>
       <c r="BK16">
-        <v>0.95499299999999998</v>
+        <v>0.954993</v>
       </c>
       <c r="BL16">
-        <v>1.0964780000000001</v>
+        <v>1.096478</v>
       </c>
       <c r="BM16">
-        <v>1.2589250000000001</v>
+        <v>1.258925</v>
       </c>
       <c r="BN16">
-        <v>1.4454400000000001</v>
+        <v>1.44544</v>
       </c>
       <c r="BO16">
-        <v>1.6595869999999999</v>
+        <v>1.659587</v>
       </c>
       <c r="BP16">
-        <v>1.9054610000000001</v>
+        <v>1.905461</v>
       </c>
       <c r="BQ16">
-        <v>2.1877620000000002</v>
+        <v>2.187762</v>
       </c>
       <c r="BR16">
-        <v>2.5118860000000001</v>
+        <v>2.511886</v>
       </c>
       <c r="BS16">
-        <v>2.8840309999999998</v>
+        <v>2.884031</v>
       </c>
       <c r="BT16">
-        <v>3.3113109999999999</v>
+        <v>3.311311</v>
       </c>
       <c r="BU16">
-        <v>3.8018939999999999</v>
+        <v>3.801894</v>
       </c>
       <c r="BV16">
-        <v>4.3651580000000001</v>
+        <v>4.365158</v>
       </c>
       <c r="BW16">
-        <v>5.0118720000000003</v>
+        <v>5.011872</v>
       </c>
       <c r="BX16">
-        <v>5.7543990000000003</v>
+        <v>5.754399</v>
       </c>
       <c r="BY16">
-        <v>6.6069339999999999</v>
+        <v>6.606934</v>
       </c>
       <c r="BZ16">
-        <v>7.5857760000000001</v>
+        <v>7.585776</v>
       </c>
       <c r="CA16">
-        <v>8.7096359999999997</v>
+        <v>8.709636</v>
       </c>
       <c r="CB16">
         <v>10</v>
@@ -4406,49 +4446,49 @@
         <v>11.481536</v>
       </c>
       <c r="CD16">
-        <v>13.182567000000001</v>
+        <v>13.182567</v>
       </c>
       <c r="CE16">
         <v>15.135612</v>
       </c>
       <c r="CF16">
-        <v>17.378008000000001</v>
+        <v>17.378008</v>
       </c>
       <c r="CG16">
-        <v>19.952622999999999</v>
+        <v>19.952623</v>
       </c>
       <c r="CH16">
-        <v>22.908677000000001</v>
+        <v>22.908677</v>
       </c>
       <c r="CI16">
-        <v>26.302679999999999</v>
+        <v>26.30268</v>
       </c>
       <c r="CJ16">
         <v>30.199517</v>
       </c>
       <c r="CK16">
-        <v>34.673684999999999</v>
+        <v>34.673685</v>
       </c>
       <c r="CL16">
-        <v>39.810716999999997</v>
+        <v>39.810717</v>
       </c>
       <c r="CM16">
-        <v>45.708818999999998</v>
+        <v>45.708819</v>
       </c>
       <c r="CN16">
-        <v>52.480746000000003</v>
+        <v>52.480746</v>
       </c>
       <c r="CO16">
-        <v>60.255958999999997</v>
+        <v>60.255959</v>
       </c>
       <c r="CP16">
-        <v>69.183097000000004</v>
+        <v>69.183097</v>
       </c>
       <c r="CQ16">
-        <v>79.432822999999999</v>
+        <v>79.432823</v>
       </c>
       <c r="CR16">
-        <v>91.201083999999994</v>
+        <v>91.201084</v>
       </c>
       <c r="CS16">
         <v>104.712855</v>
@@ -4457,120 +4497,120 @@
         <v>120.226443</v>
       </c>
       <c r="CU16">
-        <v>138.03842599999999</v>
+        <v>138.038426</v>
       </c>
       <c r="CV16">
-        <v>158.48931899999999</v>
+        <v>158.489319</v>
       </c>
       <c r="CW16">
-        <v>181.97008600000001</v>
+        <v>181.970086</v>
       </c>
       <c r="CX16">
-        <v>208.92961299999999</v>
+        <v>208.929613</v>
       </c>
       <c r="CY16">
-        <v>239.88329200000001</v>
+        <v>239.883292</v>
       </c>
       <c r="CZ16">
-        <v>275.42286999999999</v>
+        <v>275.42287</v>
       </c>
       <c r="DA16">
-        <v>316.22776599999997</v>
+        <v>316.227766</v>
       </c>
       <c r="DB16">
-        <v>363.07805500000001</v>
+        <v>363.078055</v>
       </c>
       <c r="DC16">
-        <v>416.86938300000003</v>
+        <v>416.869383</v>
       </c>
       <c r="DD16">
-        <v>478.63009199999999</v>
+        <v>478.630092</v>
       </c>
       <c r="DE16">
-        <v>549.54087400000003</v>
+        <v>549.540874</v>
       </c>
       <c r="DF16">
-        <v>630.95734400000003</v>
+        <v>630.957344</v>
       </c>
       <c r="DG16">
-        <v>724.43596000000002</v>
+        <v>724.43596</v>
       </c>
       <c r="DH16">
-        <v>831.76377100000002</v>
+        <v>831.763771</v>
       </c>
       <c r="DI16">
-        <v>954.99258599999996</v>
+        <v>954.992586</v>
       </c>
       <c r="DJ16">
         <v>1096.478196</v>
       </c>
       <c r="DK16">
-        <v>1258.9254120000001</v>
+        <v>1258.925412</v>
       </c>
       <c r="DL16">
-        <v>1445.4397710000001</v>
+        <v>1445.439771</v>
       </c>
       <c r="DM16">
-        <v>1659.5869070000001</v>
+        <v>1659.586907</v>
       </c>
       <c r="DN16">
         <v>1905.460718</v>
       </c>
       <c r="DO16">
-        <v>2187.7616240000002</v>
+        <v>2187.761624</v>
       </c>
       <c r="DP16">
-        <v>2511.8864319999998</v>
+        <v>2511.886432</v>
       </c>
       <c r="DQ16">
-        <v>2884.0315030000002</v>
+        <v>2884.031503</v>
       </c>
       <c r="DR16">
-        <v>3311.3112150000002</v>
+        <v>3311.311215</v>
       </c>
       <c r="DS16">
         <v>3801.893963</v>
       </c>
       <c r="DT16">
-        <v>4365.1583220000002</v>
+        <v>4365.158322</v>
       </c>
       <c r="DU16">
-        <v>5011.8723360000004</v>
+        <v>5011.872336</v>
       </c>
       <c r="DV16">
-        <v>5754.3993730000002</v>
+        <v>5754.399373</v>
       </c>
       <c r="DW16">
-        <v>6606.9344799999999</v>
+        <v>6606.93448</v>
       </c>
       <c r="DX16">
-        <v>7585.7757499999998</v>
+        <v>7585.77575</v>
       </c>
       <c r="DY16">
-        <v>8709.6358999999993</v>
+        <v>8709.6359</v>
       </c>
       <c r="DZ16">
         <v>10000</v>
       </c>
     </row>
-    <row r="17" spans="1:130" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>46</v>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E17" t="s">
         <v>33</v>
       </c>
       <c r="F17" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G17" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="H17" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="I17">
         <v>1.56</v>
@@ -4600,40 +4640,40 @@
         <v>40</v>
       </c>
       <c r="R17">
-        <v>10.220000000000001</v>
+        <v>10.22</v>
       </c>
       <c r="S17">
         <v>0.96</v>
       </c>
       <c r="T17">
-        <v>1.77E-2</v>
+        <v>0.0177</v>
       </c>
       <c r="U17">
-        <v>3.0960000000000001</v>
+        <v>3.096</v>
       </c>
       <c r="V17" t="s">
         <v>41</v>
       </c>
       <c r="W17">
-        <v>84.245000000000005</v>
+        <v>84.245</v>
       </c>
       <c r="X17">
         <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>0.51900000000000002</v>
+        <v>0.519</v>
       </c>
       <c r="Z17">
         <v>11.551</v>
       </c>
       <c r="AA17">
-        <v>5.4649999999999999</v>
+        <v>5.465</v>
       </c>
       <c r="AB17">
-        <v>57.786999999999999</v>
+        <v>57.787</v>
       </c>
       <c r="AC17">
-        <v>184.38399999999999</v>
+        <v>184.384</v>
       </c>
       <c r="AE17">
         <v>0</v>
@@ -4717,7 +4757,7 @@
         <v>0</v>
       </c>
       <c r="BF17">
-        <v>5.5087999999999998E-2</v>
+        <v>0.055088</v>
       </c>
       <c r="BG17">
         <v>0.182694</v>
@@ -4726,61 +4766,61 @@
         <v>0.30917</v>
       </c>
       <c r="BI17">
-        <v>0.38357400000000003</v>
+        <v>0.383574</v>
       </c>
       <c r="BJ17">
-        <v>0.42987399999999998</v>
+        <v>0.429874</v>
       </c>
       <c r="BK17">
-        <v>0.44035400000000002</v>
+        <v>0.440354</v>
       </c>
       <c r="BL17">
-        <v>0.43112099999999998</v>
+        <v>0.431121</v>
       </c>
       <c r="BM17">
-        <v>0.41732999999999998</v>
+        <v>0.41733</v>
       </c>
       <c r="BN17">
-        <v>0.41566900000000001</v>
+        <v>0.415669</v>
       </c>
       <c r="BO17">
-        <v>0.43665700000000002</v>
+        <v>0.436657</v>
       </c>
       <c r="BP17">
-        <v>0.48183100000000001</v>
+        <v>0.481831</v>
       </c>
       <c r="BQ17">
-        <v>0.54433200000000004</v>
+        <v>0.544332</v>
       </c>
       <c r="BR17">
-        <v>0.61611800000000005</v>
+        <v>0.616118</v>
       </c>
       <c r="BS17">
-        <v>0.69161099999999998</v>
+        <v>0.691611</v>
       </c>
       <c r="BT17">
-        <v>0.76744400000000002</v>
+        <v>0.767444</v>
       </c>
       <c r="BU17">
-        <v>0.84184000000000003</v>
+        <v>0.84184</v>
       </c>
       <c r="BV17">
-        <v>0.91408400000000001</v>
+        <v>0.914084</v>
       </c>
       <c r="BW17">
-        <v>0.98616999999999999</v>
+        <v>0.98617</v>
       </c>
       <c r="BX17">
         <v>1.059237</v>
       </c>
       <c r="BY17">
-        <v>1.1372819999999999</v>
+        <v>1.137282</v>
       </c>
       <c r="BZ17">
-        <v>1.2211160000000001</v>
+        <v>1.221116</v>
       </c>
       <c r="CA17">
-        <v>1.3144720000000001</v>
+        <v>1.314472</v>
       </c>
       <c r="CB17">
         <v>1.415422</v>
@@ -4789,70 +4829,70 @@
         <v>1.526632</v>
       </c>
       <c r="CD17">
-        <v>1.6438950000000001</v>
+        <v>1.643895</v>
       </c>
       <c r="CE17">
         <v>1.770993</v>
       </c>
       <c r="CF17">
-        <v>1.9073910000000001</v>
+        <v>1.907391</v>
       </c>
       <c r="CG17">
-        <v>2.0629569999999999</v>
+        <v>2.062957</v>
       </c>
       <c r="CH17">
-        <v>2.2447300000000001</v>
+        <v>2.24473</v>
       </c>
       <c r="CI17">
-        <v>2.4683679999999999</v>
+        <v>2.468368</v>
       </c>
       <c r="CJ17">
-        <v>2.7427709999999998</v>
+        <v>2.742771</v>
       </c>
       <c r="CK17">
-        <v>3.0784729999999998</v>
+        <v>3.078473</v>
       </c>
       <c r="CL17">
-        <v>3.4720810000000002</v>
+        <v>3.472081</v>
       </c>
       <c r="CM17">
-        <v>3.9119489999999999</v>
+        <v>3.911949</v>
       </c>
       <c r="CN17">
-        <v>4.3700369999999999</v>
+        <v>4.370037</v>
       </c>
       <c r="CO17">
-        <v>4.8040089999999998</v>
+        <v>4.804009</v>
       </c>
       <c r="CP17">
-        <v>5.1657690000000001</v>
+        <v>5.165769</v>
       </c>
       <c r="CQ17">
-        <v>5.4012900000000004</v>
+        <v>5.40129</v>
       </c>
       <c r="CR17">
-        <v>5.4703889999999999</v>
+        <v>5.470389</v>
       </c>
       <c r="CS17">
-        <v>5.3482229999999999</v>
+        <v>5.348223</v>
       </c>
       <c r="CT17">
-        <v>5.0321740000000004</v>
+        <v>5.032174</v>
       </c>
       <c r="CU17">
-        <v>4.5550920000000001</v>
+        <v>4.555092</v>
       </c>
       <c r="CV17">
-        <v>3.9527389999999998</v>
+        <v>3.952739</v>
       </c>
       <c r="CW17">
-        <v>3.3004690000000001</v>
+        <v>3.300469</v>
       </c>
       <c r="CX17">
-        <v>2.6389089999999999</v>
+        <v>2.638909</v>
       </c>
       <c r="CY17">
-        <v>2.0382359999999999</v>
+        <v>2.038236</v>
       </c>
       <c r="CZ17">
         <v>1.515433</v>
@@ -4861,19 +4901,19 @@
         <v>1.101709</v>
       </c>
       <c r="DB17">
-        <v>0.78912599999999999</v>
+        <v>0.789126</v>
       </c>
       <c r="DC17">
-        <v>0.57287399999999999</v>
+        <v>0.572874</v>
       </c>
       <c r="DD17">
-        <v>0.43059399999999998</v>
+        <v>0.430594</v>
       </c>
       <c r="DE17">
-        <v>0.34076200000000001</v>
+        <v>0.340762</v>
       </c>
       <c r="DF17">
-        <v>0.28102300000000002</v>
+        <v>0.281023</v>
       </c>
       <c r="DG17">
         <v>0.235349</v>
@@ -4882,7 +4922,7 @@
         <v>0.195081</v>
       </c>
       <c r="DI17">
-        <v>0.13798099999999999</v>
+        <v>0.137981</v>
       </c>
       <c r="DJ17">
         <v>0</v>
@@ -4936,24 +4976,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:130" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>46</v>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E18" t="s">
         <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G18" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="H18" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="I18">
         <v>1.56</v>
@@ -4986,22 +5026,22 @@
         <v>10.09</v>
       </c>
       <c r="S18">
-        <v>0.95199999999999996</v>
+        <v>0.952</v>
       </c>
       <c r="T18">
-        <v>1.78E-2</v>
+        <v>0.0178</v>
       </c>
       <c r="U18">
-        <v>3.1920000000000002</v>
+        <v>3.192</v>
       </c>
       <c r="V18" t="s">
         <v>41</v>
       </c>
       <c r="W18">
-        <v>87.555999999999997</v>
+        <v>87.556</v>
       </c>
       <c r="X18">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="Y18">
         <v>0.504</v>
@@ -5010,13 +5050,13 @@
         <v>11.9</v>
       </c>
       <c r="AA18">
-        <v>5.6109999999999998</v>
+        <v>5.611</v>
       </c>
       <c r="AB18">
         <v>58.06</v>
       </c>
       <c r="AC18">
-        <v>190.95500000000001</v>
+        <v>190.955</v>
       </c>
       <c r="AE18">
         <v>0</v>
@@ -5106,52 +5146,52 @@
         <v>0.166875</v>
       </c>
       <c r="BH18">
-        <v>0.30653900000000001</v>
+        <v>0.306539</v>
       </c>
       <c r="BI18">
         <v>0.371946</v>
       </c>
       <c r="BJ18">
-        <v>0.42058200000000001</v>
+        <v>0.420582</v>
       </c>
       <c r="BK18">
-        <v>0.43002699999999999</v>
+        <v>0.430027</v>
       </c>
       <c r="BL18">
-        <v>0.42157800000000001</v>
+        <v>0.421578</v>
       </c>
       <c r="BM18">
-        <v>0.40835100000000002</v>
+        <v>0.408351</v>
       </c>
       <c r="BN18">
-        <v>0.40731400000000001</v>
+        <v>0.407314</v>
       </c>
       <c r="BO18">
         <v>0.428647</v>
       </c>
       <c r="BP18">
-        <v>0.47390500000000002</v>
+        <v>0.473905</v>
       </c>
       <c r="BQ18">
-        <v>0.53632299999999999</v>
+        <v>0.536323</v>
       </c>
       <c r="BR18">
-        <v>0.60800500000000002</v>
+        <v>0.608005</v>
       </c>
       <c r="BS18">
-        <v>0.68347999999999998</v>
+        <v>0.68348</v>
       </c>
       <c r="BT18">
-        <v>0.75944999999999996</v>
+        <v>0.75945</v>
       </c>
       <c r="BU18">
-        <v>0.83419900000000002</v>
+        <v>0.834199</v>
       </c>
       <c r="BV18">
-        <v>0.90704499999999999</v>
+        <v>0.907045</v>
       </c>
       <c r="BW18">
-        <v>0.97999400000000003</v>
+        <v>0.979994</v>
       </c>
       <c r="BX18">
         <v>1.054149</v>
@@ -5160,13 +5200,13 @@
         <v>1.133472</v>
       </c>
       <c r="BZ18">
-        <v>1.2186729999999999</v>
+        <v>1.218673</v>
       </c>
       <c r="CA18">
-        <v>1.3134220000000001</v>
+        <v>1.313422</v>
       </c>
       <c r="CB18">
-        <v>1.4156569999999999</v>
+        <v>1.415657</v>
       </c>
       <c r="CC18">
         <v>1.528003</v>
@@ -5178,19 +5218,19 @@
         <v>1.77403</v>
       </c>
       <c r="CF18">
-        <v>1.9111050000000001</v>
+        <v>1.911105</v>
       </c>
       <c r="CG18">
         <v>2.067453</v>
       </c>
       <c r="CH18">
-        <v>2.2502460000000002</v>
+        <v>2.250246</v>
       </c>
       <c r="CI18">
-        <v>2.4751660000000002</v>
+        <v>2.475166</v>
       </c>
       <c r="CJ18">
-        <v>2.7508460000000001</v>
+        <v>2.750846</v>
       </c>
       <c r="CK18">
         <v>3.08724</v>
@@ -5199,34 +5239,34 @@
         <v>3.480051</v>
       </c>
       <c r="CM18">
-        <v>3.9165679999999998</v>
+        <v>3.916568</v>
       </c>
       <c r="CN18">
-        <v>4.3677929999999998</v>
+        <v>4.367793</v>
       </c>
       <c r="CO18">
-        <v>4.7909439999999996</v>
+        <v>4.790944</v>
       </c>
       <c r="CP18">
-        <v>5.1382430000000001</v>
+        <v>5.138243</v>
       </c>
       <c r="CQ18">
-        <v>5.3570970000000004</v>
+        <v>5.357097</v>
       </c>
       <c r="CR18">
-        <v>5.4092060000000002</v>
+        <v>5.409206</v>
       </c>
       <c r="CS18">
-        <v>5.2724820000000001</v>
+        <v>5.272482</v>
       </c>
       <c r="CT18">
-        <v>4.9467049999999997</v>
+        <v>4.946705</v>
       </c>
       <c r="CU18">
         <v>4.467295</v>
       </c>
       <c r="CV18">
-        <v>3.8717290000000002</v>
+        <v>3.871729</v>
       </c>
       <c r="CW18">
         <v>3.235703</v>
@@ -5238,31 +5278,31 @@
         <v>2.028505</v>
       </c>
       <c r="CZ18">
-        <v>1.5372189999999999</v>
+        <v>1.537219</v>
       </c>
       <c r="DA18">
         <v>1.151613</v>
       </c>
       <c r="DB18">
-        <v>0.86155000000000004</v>
+        <v>0.86155</v>
       </c>
       <c r="DC18">
-        <v>0.66057699999999997</v>
+        <v>0.660577</v>
       </c>
       <c r="DD18">
-        <v>0.52657200000000004</v>
+        <v>0.526572</v>
       </c>
       <c r="DE18">
-        <v>0.43892100000000001</v>
+        <v>0.438921</v>
       </c>
       <c r="DF18">
-        <v>0.37594899999999998</v>
+        <v>0.375949</v>
       </c>
       <c r="DG18">
-        <v>0.32496999999999998</v>
+        <v>0.32497</v>
       </c>
       <c r="DH18">
-        <v>0.27246500000000001</v>
+        <v>0.272465</v>
       </c>
       <c r="DI18">
         <v>0.198766</v>
@@ -5319,24 +5359,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:130" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>46</v>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E19" t="s">
         <v>33</v>
       </c>
       <c r="F19" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="G19" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H19" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="I19">
         <v>1.56</v>
@@ -5369,19 +5409,19 @@
         <v>10.01</v>
       </c>
       <c r="S19">
-        <v>0.94099999999999995</v>
+        <v>0.941</v>
       </c>
       <c r="T19">
-        <v>1.7899999999999999E-2</v>
+        <v>0.0179</v>
       </c>
       <c r="U19">
-        <v>3.1859999999999999</v>
+        <v>3.186</v>
       </c>
       <c r="V19" t="s">
         <v>41</v>
       </c>
       <c r="W19">
-        <v>87.361999999999995</v>
+        <v>87.362</v>
       </c>
       <c r="X19">
         <v>1.08</v>
@@ -5390,13 +5430,13 @@
         <v>0.497</v>
       </c>
       <c r="Z19">
-        <v>12.071999999999999</v>
+        <v>12.072</v>
       </c>
       <c r="AA19">
         <v>5.718</v>
       </c>
       <c r="AB19">
-        <v>58.603000000000002</v>
+        <v>58.603</v>
       </c>
       <c r="AC19">
         <v>192.428</v>
@@ -5489,10 +5529,10 @@
         <v>0.16177</v>
       </c>
       <c r="BH19">
-        <v>0.29841099999999998</v>
+        <v>0.298411</v>
       </c>
       <c r="BI19">
-        <v>0.36298900000000001</v>
+        <v>0.362989</v>
       </c>
       <c r="BJ19">
         <v>0.410831</v>
@@ -5504,148 +5544,148 @@
         <v>0.412464</v>
       </c>
       <c r="BM19">
-        <v>0.39993400000000001</v>
+        <v>0.399934</v>
       </c>
       <c r="BN19">
-        <v>0.39948600000000001</v>
+        <v>0.399486</v>
       </c>
       <c r="BO19">
-        <v>0.42113200000000001</v>
+        <v>0.421132</v>
       </c>
       <c r="BP19">
         <v>0.466422</v>
       </c>
       <c r="BQ19">
-        <v>0.52870300000000003</v>
+        <v>0.528703</v>
       </c>
       <c r="BR19">
-        <v>0.60018800000000005</v>
+        <v>0.600188</v>
       </c>
       <c r="BS19">
-        <v>0.67544999999999999</v>
+        <v>0.67545</v>
       </c>
       <c r="BT19">
-        <v>0.75120799999999999</v>
+        <v>0.751208</v>
       </c>
       <c r="BU19">
-        <v>0.82575900000000002</v>
+        <v>0.825759</v>
       </c>
       <c r="BV19">
         <v>0.89842</v>
       </c>
       <c r="BW19">
-        <v>0.97120399999999996</v>
+        <v>0.971204</v>
       </c>
       <c r="BX19">
         <v>1.045248</v>
       </c>
       <c r="BY19">
-        <v>1.1245609999999999</v>
+        <v>1.124561</v>
       </c>
       <c r="BZ19">
-        <v>1.2099219999999999</v>
+        <v>1.209922</v>
       </c>
       <c r="CA19">
-        <v>1.3050889999999999</v>
+        <v>1.305089</v>
       </c>
       <c r="CB19">
-        <v>1.4080710000000001</v>
+        <v>1.408071</v>
       </c>
       <c r="CC19">
         <v>1.521577</v>
       </c>
       <c r="CD19">
-        <v>1.6412949999999999</v>
+        <v>1.641295</v>
       </c>
       <c r="CE19">
-        <v>1.7710109999999999</v>
+        <v>1.771011</v>
       </c>
       <c r="CF19">
         <v>1.909975</v>
       </c>
       <c r="CG19">
-        <v>2.0678359999999998</v>
+        <v>2.067836</v>
       </c>
       <c r="CH19">
-        <v>2.2511320000000001</v>
+        <v>2.251132</v>
       </c>
       <c r="CI19">
-        <v>2.4748579999999998</v>
+        <v>2.474858</v>
       </c>
       <c r="CJ19">
-        <v>2.7470439999999998</v>
+        <v>2.747044</v>
       </c>
       <c r="CK19">
         <v>3.077302</v>
       </c>
       <c r="CL19">
-        <v>3.4616319999999998</v>
+        <v>3.461632</v>
       </c>
       <c r="CM19">
-        <v>3.8883230000000002</v>
+        <v>3.888323</v>
       </c>
       <c r="CN19">
-        <v>4.3302189999999996</v>
+        <v>4.330219</v>
       </c>
       <c r="CO19">
         <v>4.746982</v>
       </c>
       <c r="CP19">
-        <v>5.0933479999999998</v>
+        <v>5.093348</v>
       </c>
       <c r="CQ19">
-        <v>5.3187600000000002</v>
+        <v>5.31876</v>
       </c>
       <c r="CR19">
-        <v>5.3859399999999997</v>
+        <v>5.38594</v>
       </c>
       <c r="CS19">
-        <v>5.2717960000000001</v>
+        <v>5.271796</v>
       </c>
       <c r="CT19">
-        <v>4.9738280000000001</v>
+        <v>4.973828</v>
       </c>
       <c r="CU19">
-        <v>4.5226509999999998</v>
+        <v>4.522651</v>
       </c>
       <c r="CV19">
-        <v>3.9514300000000002</v>
+        <v>3.95143</v>
       </c>
       <c r="CW19">
-        <v>3.3307869999999999</v>
+        <v>3.330787</v>
       </c>
       <c r="CX19">
-        <v>2.6983579999999998</v>
+        <v>2.698358</v>
       </c>
       <c r="CY19">
-        <v>2.1203270000000001</v>
+        <v>2.120327</v>
       </c>
       <c r="CZ19">
-        <v>1.6128400000000001</v>
+        <v>1.61284</v>
       </c>
       <c r="DA19">
         <v>1.206998</v>
       </c>
       <c r="DB19">
-        <v>0.89640900000000001</v>
+        <v>0.896409</v>
       </c>
       <c r="DC19">
-        <v>0.67735500000000004</v>
+        <v>0.677355</v>
       </c>
       <c r="DD19">
-        <v>0.52753899999999998</v>
+        <v>0.527539</v>
       </c>
       <c r="DE19">
-        <v>0.42524499999999998</v>
+        <v>0.425245</v>
       </c>
       <c r="DF19">
         <v>0.347883</v>
       </c>
       <c r="DG19">
-        <v>0.28287099999999998</v>
+        <v>0.282871</v>
       </c>
       <c r="DH19">
-        <v>0.22040999999999999</v>
+        <v>0.22041</v>
       </c>
       <c r="DI19">
         <v>0.14837</v>
@@ -5702,236 +5742,243 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:130" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>63</v>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="BF20">
-        <f t="shared" ref="AF20:CQ20" si="61">AVERAGE(BF17:BF19)</f>
-        <v>1.8362666666666666E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.018362666666666666</v>
       </c>
       <c r="BG20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="1"/>
         <v>0.17044633333333334</v>
       </c>
       <c r="BH20">
-        <f t="shared" si="61"/>
-        <v>0.30470666666666668</v>
+        <f t="shared" si="1"/>
+        <v>0.3047066666666667</v>
       </c>
       <c r="BI20">
-        <f t="shared" si="61"/>
-        <v>0.37283633333333333</v>
+        <f t="shared" si="1"/>
+        <v>0.3728363333333333</v>
       </c>
       <c r="BJ20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="1"/>
         <v>0.420429</v>
       </c>
       <c r="BK20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="1"/>
         <v>0.43026300000000006</v>
       </c>
       <c r="BL20">
-        <f t="shared" si="61"/>
-        <v>0.42172100000000001</v>
+        <f t="shared" si="1"/>
+        <v>0.421721</v>
       </c>
       <c r="BM20">
-        <f t="shared" si="61"/>
-        <v>0.40853833333333328</v>
+        <f t="shared" si="1"/>
+        <v>0.4085383333333333</v>
       </c>
       <c r="BN20">
-        <f t="shared" si="61"/>
-        <v>0.40748966666666669</v>
+        <f t="shared" si="1"/>
+        <v>0.4074896666666667</v>
       </c>
       <c r="BO20">
-        <f t="shared" si="61"/>
-        <v>0.42881200000000003</v>
+        <f t="shared" si="1"/>
+        <v>0.428812</v>
       </c>
       <c r="BP20">
-        <f t="shared" si="61"/>
-        <v>0.47405266666666668</v>
+        <f t="shared" si="1"/>
+        <v>0.4740526666666667</v>
       </c>
       <c r="BQ20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="1"/>
         <v>0.5364526666666668</v>
       </c>
       <c r="BR20">
-        <f t="shared" si="61"/>
-        <v>0.60810366666666671</v>
+        <f t="shared" si="1"/>
+        <v>0.6081036666666667</v>
       </c>
       <c r="BS20">
-        <f t="shared" si="61"/>
-        <v>0.68351366666666669</v>
+        <f t="shared" si="1"/>
+        <v>0.6835136666666667</v>
       </c>
       <c r="BT20">
-        <f t="shared" si="61"/>
-        <v>0.75936733333333339</v>
+        <f t="shared" si="1"/>
+        <v>0.7593673333333334</v>
       </c>
       <c r="BU20">
-        <f t="shared" si="61"/>
-        <v>0.83393266666666666</v>
+        <f t="shared" si="1"/>
+        <v>0.8339326666666667</v>
       </c>
       <c r="BV20">
-        <f t="shared" si="61"/>
-        <v>0.90651633333333326</v>
+        <f t="shared" si="1"/>
+        <v>0.9065163333333333</v>
       </c>
       <c r="BW20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="1"/>
         <v>0.9791226666666667</v>
       </c>
       <c r="BX20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="1"/>
         <v>1.052878</v>
       </c>
       <c r="BY20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="1"/>
         <v>1.1317716666666666</v>
       </c>
       <c r="BZ20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="1"/>
         <v>1.2165703333333333</v>
       </c>
       <c r="CA20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="1"/>
         <v>1.3109943333333334</v>
       </c>
       <c r="CB20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="1"/>
         <v>1.4130500000000001</v>
       </c>
       <c r="CC20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="1"/>
         <v>1.525404</v>
       </c>
       <c r="CD20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="1"/>
         <v>1.6437899999999999</v>
       </c>
       <c r="CE20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="1"/>
         <v>1.7720113333333334</v>
       </c>
       <c r="CF20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="1"/>
         <v>1.9094903333333333</v>
       </c>
       <c r="CG20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="1"/>
         <v>2.0660819999999998</v>
       </c>
       <c r="CH20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="1"/>
         <v>2.248702666666667</v>
       </c>
       <c r="CI20">
-        <f t="shared" si="61"/>
-        <v>2.4727973333333328</v>
+        <f t="shared" si="1"/>
+        <v>2.472797333333333</v>
       </c>
       <c r="CJ20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="1"/>
         <v>2.7468869999999996</v>
       </c>
       <c r="CK20">
-        <f t="shared" si="61"/>
+        <f t="shared" si="1"/>
         <v>3.0810049999999998</v>
       </c>
       <c r="CL20">
-        <f t="shared" si="61"/>
-        <v>3.4712546666666668</v>
+        <f t="shared" si="1"/>
+        <v>3.471254666666667</v>
       </c>
       <c r="CM20">
-        <f t="shared" si="61"/>
-        <v>3.9056133333333332</v>
+        <f t="shared" si="1"/>
+        <v>3.905613333333333</v>
       </c>
       <c r="CN20">
-        <f t="shared" si="61"/>
-        <v>4.3560163333333328</v>
+        <f t="shared" si="1"/>
+        <v>4.356016333333333</v>
       </c>
       <c r="CO20">
-        <f t="shared" si="61"/>
-        <v>4.7806449999999998</v>
+        <f t="shared" si="1"/>
+        <v>4.780645</v>
       </c>
       <c r="CP20">
-        <f t="shared" si="61"/>
-        <v>5.1324533333333333</v>
+        <f t="shared" si="1"/>
+        <v>5.132453333333333</v>
       </c>
       <c r="CQ20">
-        <f t="shared" si="61"/>
-        <v>5.3590489999999997</v>
+        <f t="shared" si="1"/>
+        <v>5.359049</v>
       </c>
       <c r="CR20">
-        <f t="shared" ref="CR20:DZ20" si="62">AVERAGE(CR17:CR19)</f>
-        <v>5.4218450000000002</v>
+        <f t="shared" si="1"/>
+        <v>5.421845</v>
       </c>
       <c r="CS20">
-        <f t="shared" si="62"/>
-        <v>5.2975003333333337</v>
+        <f t="shared" si="1"/>
+        <v>5.297500333333334</v>
       </c>
       <c r="CT20">
-        <f t="shared" si="62"/>
-        <v>4.9842356666666667</v>
+        <f t="shared" si="1"/>
+        <v>4.984235666666667</v>
       </c>
       <c r="CU20">
-        <f t="shared" si="62"/>
-        <v>4.5150126666666663</v>
+        <f t="shared" si="1"/>
+        <v>4.515012666666666</v>
       </c>
       <c r="CV20">
-        <f t="shared" si="62"/>
+        <f t="shared" si="1"/>
         <v>3.9252993333333333</v>
       </c>
       <c r="CW20">
-        <f t="shared" si="62"/>
-        <v>3.2889863333333338</v>
+        <f t="shared" si="1"/>
+        <v>3.288986333333334</v>
       </c>
       <c r="CX20">
-        <f t="shared" si="62"/>
-        <v>2.6454800000000001</v>
+        <f t="shared" si="1"/>
+        <v>2.64548</v>
       </c>
       <c r="CY20">
-        <f t="shared" si="62"/>
-        <v>2.0623559999999999</v>
+        <f t="shared" si="1"/>
+        <v>2.062356</v>
       </c>
       <c r="CZ20">
-        <f t="shared" si="62"/>
+        <f t="shared" si="1"/>
         <v>1.5551640000000002</v>
       </c>
       <c r="DA20">
-        <f t="shared" si="62"/>
+        <f t="shared" si="1"/>
         <v>1.15344</v>
       </c>
       <c r="DB20">
-        <f t="shared" si="62"/>
-        <v>0.84902833333333338</v>
+        <f t="shared" si="1"/>
+        <v>0.8490283333333334</v>
       </c>
       <c r="DC20">
-        <f t="shared" si="62"/>
+        <f t="shared" si="1"/>
         <v>0.6369353333333333</v>
       </c>
       <c r="DD20">
-        <f t="shared" si="62"/>
+        <f t="shared" si="1"/>
         <v>0.49490166666666663</v>
       </c>
       <c r="DE20">
-        <f t="shared" si="62"/>
+        <f t="shared" si="1"/>
         <v>0.40164266666666665</v>
       </c>
       <c r="DF20">
-        <f t="shared" si="62"/>
+        <f t="shared" si="1"/>
         <v>0.3349516666666667</v>
       </c>
       <c r="DG20">
-        <f t="shared" si="62"/>
+        <f t="shared" si="1"/>
         <v>0.28106333333333333</v>
       </c>
       <c r="DH20">
-        <f t="shared" si="62"/>
+        <f t="shared" si="1"/>
         <v>0.22931866666666667</v>
       </c>
       <c r="DI20">
-        <f t="shared" si="62"/>
+        <f t="shared" si="1"/>
         <v>0.16170566666666666</v>
       </c>
     </row>
   </sheetData>
+  <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
+  </headerFooter>
+  <extLst/>
 </worksheet>
 </file>
--- a/Lab 3/Malvern Data/2026_SedStrat_MalvernData.xlsx
+++ b/Lab 3/Malvern Data/2026_SedStrat_MalvernData.xlsx
@@ -175,7 +175,7 @@
     <t>Thursday, September 17, 2026 1:52:53 PM</t>
   </si>
   <si>
-    <t>Lab Group 1</t>
+    <t>Group 1</t>
   </si>
   <si>
     <t>SedStrat2026Grp2</t>
@@ -205,7 +205,7 @@
     <t>Thursday, September 17, 2026 1:13:11 PM</t>
   </si>
   <si>
-    <t>Lab Group 2</t>
+    <t>Group 2</t>
   </si>
   <si>
     <t>SedStrat2026Grp3</t>
@@ -229,7 +229,7 @@
     <t>Thursday, September 17, 2026 1:26:11 PM</t>
   </si>
   <si>
-    <t>Group 3</t>
+    <t>Hoff-Reed Lab Group</t>
   </si>
 </sst>
 </file>
@@ -621,7 +621,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{6234606E-39E7-47EA-8B0F-133B4D4F6EC6}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{73A2E2DD-BECE-4205-89C3-2C370FBDEE6F}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:EA20"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="8.8515625" customHeight="1"/>
   <sheetData>
@@ -5974,7 +5974,7 @@
   </sheetData>
   <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
+  <pageSetup paperSize="1" pageOrder="downThenOver" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
     <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
